--- a/SuppXLS/Scen_z_MACC-RSD-CAPs.xlsx
+++ b/SuppXLS/Scen_z_MACC-RSD-CAPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14397682-CD16-4FD3-B429-4E3C86978315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3648DC4-7B5E-4D5A-A228-875D5325D9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="186">
   <si>
     <t>Sum of Pv</t>
   </si>
@@ -611,6 +611,9 @@
   </si>
   <si>
     <t>R-SW_Apt_HET_N1, R-SW_Apt_HET_N2, R-SW_Att_HET_N1, R-SW_Att_HET_N2, R-SW_Det_HET_N1, R-SW_Det_HET_N2</t>
+  </si>
+  <si>
+    <t>R-SH_Det_ELC_HPN2-AB, R-SH_Det_ELC_HPN2-C, R-SH_Det_ELC_HPN2-D, R-SH_Det_ELC_HPN2-E, R-SH_Det_ELC_HPN2-F, R-SH_Det_ELC_HPN2-G, R-SH_Det_ELC_HPN3-AB, R-SH_Det_ELC_HPN3-C, R-SH_Det_ELC_HPN3-D, R-SH_Det_ELC_HPN3-E, R-SH_Det_ELC_HPN3-F, R-SH_Det_ELC_HPN3-G, R-SW_Det_ELC_HPN1-AB, R-SW_Det_ELC_HPN1-C, R-SW_Det_ELC_HPN1-D, R-SW_Det_ELC_HPN1-E, R-SW_Det_ELC_HPN1-F, R-SW_Det_ELC_HPN1-G, R-SW_Det_ELC_HPN2-AB, R-SW_Det_ELC_HPN2-C, R-SW_Det_ELC_HPN2-D, R-SW_Det_ELC_HPN2-E, R-SW_Det_ELC_HPN2-F, R-SW_Det_ELC_HPN2-G, R-SW_Det_GAS_HHPN1, R-SW_Det_GAS_HPN1</t>
   </si>
 </sst>
 </file>
@@ -620,7 +623,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -813,6 +816,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="39">
@@ -1683,20 +1691,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN25"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AR25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="35" width="17.140625" bestFit="1"/>
+    <col min="1" max="2" width="17.109375" bestFit="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="35" width="17.109375" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="D2" s="4">
         <v>2019</v>
       </c>
@@ -1794,7 +1804,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>176</v>
       </c>
@@ -1805,135 +1815,135 @@
         <v>168</v>
       </c>
       <c r="D3" cm="1">
-        <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
+        <v>7.4972968400410007</v>
+      </c>
+      <c r="E3" cm="1">
+        <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
         <v>6.4511985452419092</v>
       </c>
-      <c r="E3" cm="1">
-        <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
+      <c r="F3" cm="1">
+        <f t="array" aca="1" ref="F3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
         <v>0</v>
       </c>
-      <c r="F3" cm="1">
-        <f t="array" aca="1" ref="F3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
+      <c r="G3" cm="1">
+        <f t="array" aca="1" ref="G3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
         <v>0</v>
       </c>
-      <c r="G3" cm="1">
-        <f t="array" aca="1" ref="G3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
+      <c r="H3" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
         <v>0</v>
       </c>
-      <c r="H3" cm="1">
-        <f t="array" aca="1" ref="H3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
+      <c r="I3" cm="1">
+        <f t="array" aca="1" ref="I3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
         <v>0</v>
       </c>
-      <c r="I3" cm="1">
-        <f t="array" aca="1" ref="I3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+      <c r="J3" cm="1">
+        <f t="array" aca="1" ref="J3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
         <v>0</v>
       </c>
-      <c r="J3" cm="1">
-        <f t="array" aca="1" ref="J3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
+      <c r="K3" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
         <v>0</v>
       </c>
-      <c r="K3" cm="1">
-        <f t="array" aca="1" ref="K3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+      <c r="L3" cm="1">
+        <f t="array" aca="1" ref="L3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
         <v>0</v>
       </c>
-      <c r="L3" cm="1">
-        <f t="array" aca="1" ref="L3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+      <c r="M3" cm="1">
+        <f t="array" aca="1" ref="M3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
         <v>0</v>
       </c>
-      <c r="M3" cm="1">
-        <f t="array" aca="1" ref="M3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+      <c r="N3" cm="1">
+        <f t="array" aca="1" ref="N3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
         <v>0</v>
       </c>
-      <c r="N3" cm="1">
-        <f t="array" aca="1" ref="N3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+      <c r="O3" cm="1">
+        <f t="array" aca="1" ref="O3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
         <v>0</v>
       </c>
-      <c r="O3" cm="1">
-        <f t="array" aca="1" ref="O3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
+      <c r="P3" cm="1">
+        <f t="array" aca="1" ref="P3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
         <v>0</v>
       </c>
-      <c r="P3" cm="1">
-        <f t="array" aca="1" ref="P3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+      <c r="Q3" cm="1">
+        <f t="array" aca="1" ref="Q3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
         <v>0.44463604711407601</v>
       </c>
-      <c r="Q3" cm="1">
-        <f t="array" aca="1" ref="Q3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+      <c r="R3" cm="1">
+        <f t="array" aca="1" ref="R3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
         <v>0.46046896912073598</v>
       </c>
-      <c r="R3" cm="1">
-        <f t="array" aca="1" ref="R3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
+      <c r="S3" cm="1">
+        <f t="array" aca="1" ref="S3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
         <v>0.46046900129749269</v>
       </c>
-      <c r="S3" cm="1">
-        <f t="array" aca="1" ref="S3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+      <c r="T3" cm="1">
+        <f t="array" aca="1" ref="T3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
         <v>2.4206011625898549</v>
       </c>
-      <c r="T3" cm="1">
-        <f t="array" aca="1" ref="T3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
+      <c r="U3" cm="1">
+        <f t="array" aca="1" ref="U3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
         <v>2.4206010840894598</v>
       </c>
-      <c r="U3" cm="1">
-        <f t="array" aca="1" ref="U3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
+      <c r="V3" cm="1">
+        <f t="array" aca="1" ref="V3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
         <v>2.4364326056131591</v>
       </c>
-      <c r="V3" cm="1">
-        <f t="array" aca="1" ref="V3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
+      <c r="W3" cm="1">
+        <f t="array" aca="1" ref="W3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
         <v>2.4364340125859707</v>
       </c>
-      <c r="W3" cm="1">
-        <f t="array" aca="1" ref="W3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
+      <c r="X3" cm="1">
+        <f t="array" aca="1" ref="X3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
         <v>2.4364340255450156</v>
       </c>
-      <c r="X3" cm="1">
-        <f t="array" aca="1" ref="X3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
+      <c r="Y3" cm="1">
+        <f t="array" aca="1" ref="Y3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
         <v>2.4364340108380134</v>
       </c>
-      <c r="Y3" cm="1">
-        <f t="array" aca="1" ref="Y3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
+      <c r="Z3" cm="1">
+        <f t="array" aca="1" ref="Z3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
         <v>2.4364340281442716</v>
       </c>
-      <c r="Z3" cm="1">
-        <f t="array" aca="1" ref="Z3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
+      <c r="AA3" cm="1">
+        <f t="array" aca="1" ref="AA3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
         <v>2.4364340278843595</v>
       </c>
-      <c r="AA3" cm="1">
-        <f t="array" aca="1" ref="AA3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
+      <c r="AB3" cm="1">
+        <f t="array" aca="1" ref="AB3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
         <v>2.4364340243871569</v>
       </c>
-      <c r="AB3" cm="1">
-        <f t="array" aca="1" ref="AB3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
+      <c r="AC3" cm="1">
+        <f t="array" aca="1" ref="AC3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
         <v>2.4364340205331261</v>
       </c>
-      <c r="AC3" cm="1">
-        <f t="array" aca="1" ref="AC3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
+      <c r="AD3" cm="1">
+        <f t="array" aca="1" ref="AD3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
         <v>2.4364340182865707</v>
       </c>
-      <c r="AD3" cm="1">
-        <f t="array" aca="1" ref="AD3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
+      <c r="AE3" cm="1">
+        <f t="array" aca="1" ref="AE3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
         <v>2.4364340118990979</v>
       </c>
-      <c r="AE3" cm="1">
-        <f t="array" aca="1" ref="AE3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
+      <c r="AF3" cm="1">
+        <f t="array" aca="1" ref="AF3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
         <v>2.4364340216575533</v>
       </c>
-      <c r="AF3" cm="1">
-        <f t="array" aca="1" ref="AF3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
+      <c r="AG3" cm="1">
+        <f t="array" aca="1" ref="AG3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
         <v>2.4364340366515318</v>
       </c>
-      <c r="AG3" cm="1">
-        <f t="array" aca="1" ref="AG3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
+      <c r="AH3" cm="1">
+        <f t="array" aca="1" ref="AH3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
         <v>2.4364340343988853</v>
       </c>
-      <c r="AH3" cm="1">
-        <f t="array" aca="1" ref="AH3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
+      <c r="AI3" cm="1">
+        <f t="array" aca="1" ref="AI3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
         <v>2.4364340237577919</v>
       </c>
-      <c r="AI3" cm="1">
-        <f t="array" aca="1" ref="AI3" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C3,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AI:AI))</f>
-        <v>2.4364340501266972</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>177</v>
       </c>
@@ -1943,76 +1953,76 @@
       <c r="C4" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D4" cm="1">
-        <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+      <c r="E4" cm="1">
+        <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
         <v>3.658449809291918</v>
       </c>
-      <c r="E4" cm="1">
-        <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
+      <c r="F4" cm="1">
+        <f t="array" aca="1" ref="F4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
         <v>25.399042121578887</v>
       </c>
-      <c r="F4" cm="1">
-        <f t="array" aca="1" ref="F4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
+      <c r="G4" cm="1">
+        <f t="array" aca="1" ref="G4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
         <v>37.836289178591535</v>
       </c>
-      <c r="G4" cm="1">
-        <f t="array" aca="1" ref="G4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
+      <c r="H4" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
         <v>0</v>
       </c>
-      <c r="H4" cm="1">
-        <f t="array" aca="1" ref="H4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
+      <c r="I4" cm="1">
+        <f t="array" aca="1" ref="I4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
         <v>0</v>
       </c>
-      <c r="I4" cm="1">
-        <f t="array" aca="1" ref="I4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+      <c r="J4" cm="1">
+        <f t="array" aca="1" ref="J4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
         <v>7.2471677251001623</v>
       </c>
-      <c r="J4" cm="1">
-        <f t="array" aca="1" ref="J4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
+      <c r="K4" cm="1">
+        <f t="array" aca="1" ref="K4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
         <v>22.364961381905236</v>
       </c>
-      <c r="K4" cm="1">
-        <f t="array" aca="1" ref="K4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+      <c r="L4" cm="1">
+        <f t="array" aca="1" ref="L4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
         <v>7.3921218303180929</v>
       </c>
-      <c r="L4" cm="1">
-        <f t="array" aca="1" ref="L4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+      <c r="M4" cm="1">
+        <f t="array" aca="1" ref="M4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
         <v>3.1129013029099921</v>
       </c>
-      <c r="M4" cm="1">
-        <f t="array" aca="1" ref="M4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+      <c r="N4" cm="1">
+        <f t="array" aca="1" ref="N4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
         <v>3.1129013032204691</v>
       </c>
-      <c r="N4" cm="1">
-        <f t="array" aca="1" ref="N4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+      <c r="O4" cm="1">
+        <f t="array" aca="1" ref="O4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
         <v>0.69717872733106501</v>
       </c>
-      <c r="O4" cm="1">
-        <f t="array" aca="1" ref="O4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
+      <c r="P4" cm="1">
+        <f t="array" aca="1" ref="P4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
         <v>0</v>
       </c>
-      <c r="P4" cm="1">
-        <f t="array" aca="1" ref="P4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+      <c r="Q4" cm="1">
+        <f t="array" aca="1" ref="Q4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
         <v>3.1665838872884801E-2</v>
       </c>
-      <c r="Q4" cm="1">
-        <f t="array" aca="1" ref="Q4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+      <c r="R4" cm="1">
+        <f t="array" aca="1" ref="R4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
         <v>1.5832931196827299E-2</v>
       </c>
-      <c r="R4" cm="1">
-        <f t="array" aca="1" ref="R4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
+      <c r="S4" cm="1">
+        <f t="array" aca="1" ref="S4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
         <v>1.5832923423522299E-2</v>
       </c>
-      <c r="S4" cm="1">
-        <f t="array" aca="1" ref="S4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+      <c r="T4" cm="1">
+        <f t="array" aca="1" ref="T4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
         <v>1.5832880072042099E-2</v>
       </c>
-      <c r="T4" cm="1">
-        <f t="array" aca="1" ref="T4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
+      <c r="U4" cm="1">
+        <f t="array" aca="1" ref="U4" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C4,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
         <v>1.5832962705996999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>178</v>
       </c>
@@ -2023,83 +2033,87 @@
         <v>183</v>
       </c>
       <c r="D5" cm="1">
-        <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
         <v>0</v>
       </c>
-      <c r="F5" cm="1">
-        <f t="array" aca="1" ref="F5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
+      <c r="E5" cm="1">
+        <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" cm="1">
+        <f t="array" aca="1" ref="G5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
         <v>3.8060493142390714</v>
       </c>
-      <c r="I5" cm="1">
-        <f t="array" aca="1" ref="I5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+      <c r="J5" cm="1">
+        <f t="array" aca="1" ref="J5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
         <v>20.788282619861675</v>
       </c>
-      <c r="J5" cm="1">
-        <f t="array" aca="1" ref="J5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
+      <c r="K5" cm="1">
+        <f t="array" aca="1" ref="K5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
         <v>17.116403534175284</v>
       </c>
-      <c r="K5" cm="1">
-        <f t="array" aca="1" ref="K5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+      <c r="L5" cm="1">
+        <f t="array" aca="1" ref="L5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
         <v>0.10122870843971581</v>
       </c>
-      <c r="L5" cm="1">
-        <f t="array" aca="1" ref="L5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+      <c r="M5" cm="1">
+        <f t="array" aca="1" ref="M5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
         <v>9.7261719132753124E-2</v>
       </c>
-      <c r="M5" cm="1">
-        <f t="array" aca="1" ref="M5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+      <c r="N5" cm="1">
+        <f t="array" aca="1" ref="N5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
         <v>9.183375394827363E-2</v>
       </c>
-      <c r="N5" cm="1">
-        <f t="array" aca="1" ref="N5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+      <c r="O5" cm="1">
+        <f t="array" aca="1" ref="O5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
         <v>8.6427548778169008E-2</v>
       </c>
-      <c r="O5" cm="1">
-        <f t="array" aca="1" ref="O5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
+      <c r="P5" cm="1">
+        <f t="array" aca="1" ref="P5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
         <v>4.0535264804595168E-3</v>
       </c>
-      <c r="P5" cm="1">
-        <f t="array" aca="1" ref="P5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+      <c r="Q5" cm="1">
+        <f t="array" aca="1" ref="Q5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
         <v>0.32227998351670517</v>
       </c>
-      <c r="Q5" cm="1">
-        <f t="array" aca="1" ref="Q5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+      <c r="R5" cm="1">
+        <f t="array" aca="1" ref="R5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
         <v>0.13578381309056742</v>
       </c>
-      <c r="S5" cm="1">
-        <f t="array" aca="1" ref="S5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+      <c r="T5" cm="1">
+        <f t="array" aca="1" ref="T5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
         <v>4.0533582495780231E-3</v>
       </c>
-      <c r="AB5" cm="1">
-        <f t="array" aca="1" ref="AB5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
+      <c r="AC5" cm="1">
+        <f t="array" aca="1" ref="AC5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
         <v>1.5218449798815394</v>
       </c>
-      <c r="AC5" cm="1">
-        <f t="array" aca="1" ref="AC5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
+      <c r="AD5" cm="1">
+        <f t="array" aca="1" ref="AD5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
         <v>18.024512011764671</v>
       </c>
-      <c r="AD5" cm="1">
-        <f t="array" aca="1" ref="AD5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
+      <c r="AE5" cm="1">
+        <f t="array" aca="1" ref="AE5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
         <v>19.424702194124897</v>
       </c>
-      <c r="AE5" cm="1">
-        <f t="array" aca="1" ref="AE5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
+      <c r="AF5" cm="1">
+        <f t="array" aca="1" ref="AF5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
         <v>0.25204396562617726</v>
       </c>
-      <c r="AF5" cm="1">
-        <f t="array" aca="1" ref="AF5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
+      <c r="AG5" cm="1">
+        <f t="array" aca="1" ref="AG5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
         <v>0.24822133354915377</v>
       </c>
-      <c r="AG5" cm="1">
-        <f t="array" aca="1" ref="AG5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
+      <c r="AH5" cm="1">
+        <f t="array" aca="1" ref="AH5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
         <v>0.24253002053769299</v>
       </c>
-      <c r="AH5" cm="1">
-        <f t="array" aca="1" ref="AH5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
+      <c r="AI5" cm="1">
+        <f t="array" aca="1" ref="AI5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
         <v>0.23673320957000143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>179</v>
       </c>
@@ -2110,135 +2124,135 @@
         <v>173</v>
       </c>
       <c r="D6" cm="1">
-        <f t="array" aca="1" ref="D6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <f t="array" aca="1" ref="D6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
         <v>0</v>
       </c>
       <c r="E6" cm="1">
-        <f t="array" aca="1" ref="E6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
+        <f t="array" aca="1" ref="E6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
         <v>0</v>
       </c>
       <c r="F6" cm="1">
-        <f t="array" aca="1" ref="F6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
+        <f t="array" aca="1" ref="F6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
         <v>0</v>
       </c>
       <c r="G6" cm="1">
-        <f t="array" aca="1" ref="G6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
+        <f t="array" aca="1" ref="G6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
         <v>0</v>
       </c>
       <c r="H6" cm="1">
-        <f t="array" aca="1" ref="H6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
+        <f t="array" aca="1" ref="H6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
         <v>0</v>
       </c>
       <c r="I6" cm="1">
-        <f t="array" aca="1" ref="I6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+        <f t="array" aca="1" ref="I6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
         <v>0</v>
       </c>
       <c r="J6" cm="1">
-        <f t="array" aca="1" ref="J6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
+        <f t="array" aca="1" ref="J6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
         <v>0</v>
       </c>
       <c r="K6" cm="1">
-        <f t="array" aca="1" ref="K6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+        <f t="array" aca="1" ref="K6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
         <v>0</v>
       </c>
       <c r="L6" cm="1">
-        <f t="array" aca="1" ref="L6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+        <f t="array" aca="1" ref="L6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
         <v>0</v>
       </c>
       <c r="M6" cm="1">
-        <f t="array" aca="1" ref="M6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+        <f t="array" aca="1" ref="M6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
         <v>0</v>
       </c>
       <c r="N6" cm="1">
-        <f t="array" aca="1" ref="N6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+        <f t="array" aca="1" ref="N6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
         <v>0</v>
       </c>
       <c r="O6" cm="1">
-        <f t="array" aca="1" ref="O6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
+        <f t="array" aca="1" ref="O6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
         <v>0</v>
       </c>
       <c r="P6" cm="1">
-        <f t="array" aca="1" ref="P6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+        <f t="array" aca="1" ref="P6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
         <v>0</v>
       </c>
       <c r="Q6" cm="1">
-        <f t="array" aca="1" ref="Q6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+        <f t="array" aca="1" ref="Q6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
         <v>0</v>
       </c>
       <c r="R6" cm="1">
-        <f t="array" aca="1" ref="R6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
+        <f t="array" aca="1" ref="R6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
         <v>0</v>
       </c>
       <c r="S6" cm="1">
-        <f t="array" aca="1" ref="S6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+        <f t="array" aca="1" ref="S6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
         <v>0</v>
       </c>
       <c r="T6" cm="1">
-        <f t="array" aca="1" ref="T6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
+        <f t="array" aca="1" ref="T6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
         <v>0</v>
       </c>
       <c r="U6" cm="1">
-        <f t="array" aca="1" ref="U6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
+        <f t="array" aca="1" ref="U6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
         <v>0</v>
       </c>
       <c r="V6" cm="1">
-        <f t="array" aca="1" ref="V6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
+        <f t="array" aca="1" ref="V6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
         <v>0</v>
       </c>
       <c r="W6" cm="1">
-        <f t="array" aca="1" ref="W6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
+        <f t="array" aca="1" ref="W6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
         <v>0</v>
       </c>
       <c r="X6" cm="1">
-        <f t="array" aca="1" ref="X6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
+        <f t="array" aca="1" ref="X6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
         <v>0</v>
       </c>
       <c r="Y6" cm="1">
-        <f t="array" aca="1" ref="Y6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
+        <f t="array" aca="1" ref="Y6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
         <v>0</v>
       </c>
       <c r="Z6" cm="1">
-        <f t="array" aca="1" ref="Z6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
+        <f t="array" aca="1" ref="Z6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
         <v>0</v>
       </c>
       <c r="AA6" cm="1">
-        <f t="array" aca="1" ref="AA6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
+        <f t="array" aca="1" ref="AA6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
         <v>0</v>
       </c>
       <c r="AB6" cm="1">
-        <f t="array" aca="1" ref="AB6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
+        <f t="array" aca="1" ref="AB6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
         <v>0</v>
       </c>
       <c r="AC6" cm="1">
-        <f t="array" aca="1" ref="AC6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
+        <f t="array" aca="1" ref="AC6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
         <v>0</v>
       </c>
       <c r="AD6" cm="1">
-        <f t="array" aca="1" ref="AD6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
+        <f t="array" aca="1" ref="AD6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
         <v>0</v>
       </c>
       <c r="AE6" cm="1">
-        <f t="array" aca="1" ref="AE6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
+        <f t="array" aca="1" ref="AE6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
         <v>0</v>
       </c>
       <c r="AF6" cm="1">
-        <f t="array" aca="1" ref="AF6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
+        <f t="array" aca="1" ref="AF6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
         <v>0</v>
       </c>
       <c r="AG6" cm="1">
-        <f t="array" aca="1" ref="AG6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
+        <f t="array" aca="1" ref="AG6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
         <v>0</v>
       </c>
       <c r="AH6" cm="1">
-        <f t="array" aca="1" ref="AH6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
+        <f t="array" aca="1" ref="AH6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
         <v>0</v>
       </c>
       <c r="AI6" cm="1">
-        <f t="array" aca="1" ref="AI6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AI:AI))</f>
+        <f t="array" aca="1" ref="AI6" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C6,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>180</v>
       </c>
@@ -2249,131 +2263,135 @@
         <v>182</v>
       </c>
       <c r="D7" cm="1">
-        <f t="array" aca="1" ref="D7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <f t="array" aca="1" ref="D7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
+        <v>6.1992245020532222</v>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" aca="1" ref="E7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
         <v>52.486207295833736</v>
       </c>
-      <c r="E7" cm="1">
-        <f t="array" aca="1" ref="E7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
+      <c r="F7" cm="1">
+        <f t="array" aca="1" ref="F7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
         <v>48.139252575999855</v>
       </c>
       <c r="G7" cm="1">
-        <f t="array" aca="1" ref="G7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
+        <f t="array" aca="1" ref="G7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
+        <v>48.176539084588171</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" aca="1" ref="H7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
         <v>47.254031061643474</v>
       </c>
-      <c r="H7" cm="1">
-        <f t="array" aca="1" ref="H7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
+      <c r="I7" cm="1">
+        <f t="array" aca="1" ref="I7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
         <v>36.341222060544069</v>
       </c>
-      <c r="I7" cm="1">
-        <f t="array" aca="1" ref="I7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+      <c r="J7" cm="1">
+        <f t="array" aca="1" ref="J7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
         <v>34.001223396749722</v>
       </c>
-      <c r="J7" cm="1">
-        <f t="array" aca="1" ref="J7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
+      <c r="K7" cm="1">
+        <f t="array" aca="1" ref="K7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
         <v>19.832350036052215</v>
       </c>
-      <c r="K7" cm="1">
-        <f t="array" aca="1" ref="K7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+      <c r="L7" cm="1">
+        <f t="array" aca="1" ref="L7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
         <v>0.58261382233976577</v>
       </c>
-      <c r="L7" cm="1">
-        <f t="array" aca="1" ref="L7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+      <c r="M7" cm="1">
+        <f t="array" aca="1" ref="M7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
         <v>0.62415261350705342</v>
       </c>
-      <c r="M7" cm="1">
-        <f t="array" aca="1" ref="M7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+      <c r="N7" cm="1">
+        <f t="array" aca="1" ref="N7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
         <v>0.63315861270565099</v>
       </c>
-      <c r="N7" cm="1">
-        <f t="array" aca="1" ref="N7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+      <c r="O7" cm="1">
+        <f t="array" aca="1" ref="O7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
         <v>0.63217534356507876</v>
       </c>
-      <c r="O7" cm="1">
-        <f t="array" aca="1" ref="O7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
+      <c r="P7" cm="1">
+        <f t="array" aca="1" ref="P7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
         <v>0.46476519170158559</v>
       </c>
-      <c r="P7" cm="1">
-        <f t="array" aca="1" ref="P7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+      <c r="Q7" cm="1">
+        <f t="array" aca="1" ref="Q7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
         <v>4.7339116770476313</v>
       </c>
-      <c r="Q7" cm="1">
-        <f t="array" aca="1" ref="Q7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+      <c r="R7" cm="1">
+        <f t="array" aca="1" ref="R7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
         <v>4.4787925911548054</v>
       </c>
-      <c r="R7" cm="1">
-        <f t="array" aca="1" ref="R7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
+      <c r="S7" cm="1">
+        <f t="array" aca="1" ref="S7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
         <v>0.54255292628316576</v>
       </c>
-      <c r="S7" cm="1">
-        <f t="array" aca="1" ref="S7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+      <c r="T7" cm="1">
+        <f t="array" aca="1" ref="T7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
         <v>0.51895152462753369</v>
       </c>
-      <c r="T7" cm="1">
-        <f t="array" aca="1" ref="T7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
+      <c r="U7" cm="1">
+        <f t="array" aca="1" ref="U7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
         <v>10.607764901314365</v>
       </c>
-      <c r="U7" cm="1">
-        <f t="array" aca="1" ref="U7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
+      <c r="V7" cm="1">
+        <f t="array" aca="1" ref="V7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
         <v>10.684082448510717</v>
       </c>
-      <c r="V7" cm="1">
-        <f t="array" aca="1" ref="V7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
+      <c r="W7" cm="1">
+        <f t="array" aca="1" ref="W7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
         <v>11.399739886893032</v>
       </c>
-      <c r="W7" cm="1">
-        <f t="array" aca="1" ref="W7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
+      <c r="X7" cm="1">
+        <f t="array" aca="1" ref="X7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
         <v>12.110285847437895</v>
       </c>
-      <c r="X7" cm="1">
-        <f t="array" aca="1" ref="X7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
+      <c r="Y7" cm="1">
+        <f t="array" aca="1" ref="Y7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
         <v>59.873935220796213</v>
       </c>
-      <c r="Y7" cm="1">
-        <f t="array" aca="1" ref="Y7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
+      <c r="Z7" cm="1">
+        <f t="array" aca="1" ref="Z7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
         <v>47.45538608557677</v>
       </c>
-      <c r="Z7" cm="1">
-        <f t="array" aca="1" ref="Z7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
+      <c r="AA7" cm="1">
+        <f t="array" aca="1" ref="AA7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
         <v>47.492670285387476</v>
       </c>
-      <c r="AA7" cm="1">
-        <f t="array" aca="1" ref="AA7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
+      <c r="AB7" cm="1">
+        <f t="array" aca="1" ref="AB7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
         <v>46.830456717507921</v>
       </c>
-      <c r="AB7" cm="1">
-        <f t="array" aca="1" ref="AB7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
+      <c r="AC7" cm="1">
+        <f t="array" aca="1" ref="AC7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
         <v>35.901575389164407</v>
       </c>
-      <c r="AC7" cm="1">
-        <f t="array" aca="1" ref="AC7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
+      <c r="AD7" cm="1">
+        <f t="array" aca="1" ref="AD7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
         <v>33.544660014970368</v>
       </c>
-      <c r="AD7" cm="1">
-        <f t="array" aca="1" ref="AD7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
+      <c r="AE7" cm="1">
+        <f t="array" aca="1" ref="AE7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
         <v>19.367588868308498</v>
       </c>
-      <c r="AE7" cm="1">
-        <f t="array" aca="1" ref="AE7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
+      <c r="AF7" cm="1">
+        <f t="array" aca="1" ref="AF7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
         <v>2.2877872170714868</v>
       </c>
-      <c r="AF7" cm="1">
-        <f t="array" aca="1" ref="AF7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
+      <c r="AG7" cm="1">
+        <f t="array" aca="1" ref="AG7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
         <v>0.92469243365947229</v>
       </c>
-      <c r="AG7" cm="1">
-        <f t="array" aca="1" ref="AG7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
+      <c r="AH7" cm="1">
+        <f t="array" aca="1" ref="AH7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
         <v>3.1937179787145529</v>
       </c>
-      <c r="AH7" cm="1">
-        <f t="array" aca="1" ref="AH7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
+      <c r="AI7" cm="1">
+        <f t="array" aca="1" ref="AI7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
         <v>0.95594928565225012</v>
       </c>
-      <c r="AI7" cm="1">
-        <f t="array" aca="1" ref="AI7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AI:AI))</f>
-        <v>0.6409026986153924</v>
-      </c>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>181</v>
       </c>
@@ -2384,107 +2402,246 @@
         <v>175</v>
       </c>
       <c r="D8" cm="1">
-        <f t="array" aca="1" ref="D8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <f t="array" aca="1" ref="D8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
         <v>0</v>
       </c>
-      <c r="G8" cm="1">
-        <f t="array" aca="1" ref="G8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
+      <c r="E8" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" cm="1">
+        <f t="array" aca="1" ref="H8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
         <v>0.30981051123868997</v>
       </c>
-      <c r="H8" cm="1">
-        <f t="array" aca="1" ref="H8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
+      <c r="I8" cm="1">
+        <f t="array" aca="1" ref="I8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
         <v>3.5732957087922799</v>
       </c>
-      <c r="I8" cm="1">
-        <f t="array" aca="1" ref="I8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+      <c r="J8" cm="1">
+        <f t="array" aca="1" ref="J8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
         <v>1.435171964996264</v>
       </c>
-      <c r="K8" cm="1">
-        <f t="array" aca="1" ref="K8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+      <c r="L8" cm="1">
+        <f t="array" aca="1" ref="L8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
         <v>0.89317594739064299</v>
       </c>
-      <c r="L8" cm="1">
-        <f t="array" aca="1" ref="L8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+      <c r="M8" cm="1">
+        <f t="array" aca="1" ref="M8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
         <v>0.7222118041341421</v>
       </c>
-      <c r="M8" cm="1">
-        <f t="array" aca="1" ref="M8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+      <c r="N8" cm="1">
+        <f t="array" aca="1" ref="N8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
         <v>4.9216740506540502</v>
       </c>
-      <c r="N8" cm="1">
-        <f t="array" aca="1" ref="N8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+      <c r="O8" cm="1">
+        <f t="array" aca="1" ref="O8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
         <v>1.2658375566048812</v>
       </c>
-      <c r="P8" cm="1">
-        <f t="array" aca="1" ref="P8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+      <c r="Q8" cm="1">
+        <f t="array" aca="1" ref="Q8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
         <v>2.6974966375748197</v>
       </c>
-      <c r="Q8" cm="1">
-        <f t="array" aca="1" ref="Q8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+      <c r="R8" cm="1">
+        <f t="array" aca="1" ref="R8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
         <v>3.5008444071753502</v>
       </c>
-      <c r="R8" cm="1">
-        <f t="array" aca="1" ref="R8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
+      <c r="S8" cm="1">
+        <f t="array" aca="1" ref="S8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
         <v>3.6729574578571897</v>
       </c>
-      <c r="S8" cm="1">
-        <f t="array" aca="1" ref="S8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+      <c r="T8" cm="1">
+        <f t="array" aca="1" ref="T8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
         <v>3.6747754546337799</v>
       </c>
-      <c r="T8" cm="1">
-        <f t="array" aca="1" ref="T8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
+      <c r="U8" cm="1">
+        <f t="array" aca="1" ref="U8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
         <v>3.6812978416712498</v>
       </c>
-      <c r="U8" cm="1">
-        <f t="array" aca="1" ref="U8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
+      <c r="V8" cm="1">
+        <f t="array" aca="1" ref="V8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
         <v>3.69741195771975</v>
       </c>
-      <c r="V8" cm="1">
-        <f t="array" aca="1" ref="V8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
+      <c r="W8" cm="1">
+        <f t="array" aca="1" ref="W8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
         <v>3.7074573520362799</v>
       </c>
-      <c r="W8" cm="1">
-        <f t="array" aca="1" ref="W8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
+      <c r="X8" cm="1">
+        <f t="array" aca="1" ref="X8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
         <v>0.6289541007244579</v>
       </c>
-      <c r="X8" cm="1">
-        <f t="array" aca="1" ref="X8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
+      <c r="Y8" cm="1">
+        <f t="array" aca="1" ref="Y8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
         <v>0.50563414364917003</v>
       </c>
-      <c r="Y8" cm="1">
-        <f t="array" aca="1" ref="Y8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
+      <c r="Z8" cm="1">
+        <f t="array" aca="1" ref="Z8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
         <v>0.1456591625271445</v>
       </c>
-      <c r="AC8" cm="1">
-        <f t="array" aca="1" ref="AC8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
+      <c r="AD8" cm="1">
+        <f t="array" aca="1" ref="AD8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
         <v>1.3464678774611289</v>
       </c>
-      <c r="AD8" cm="1">
-        <f t="array" aca="1" ref="AD8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
+      <c r="AE8" cm="1">
+        <f t="array" aca="1" ref="AE8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
         <v>0.72456075010836396</v>
       </c>
-      <c r="AE8" cm="1">
-        <f t="array" aca="1" ref="AE8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
+      <c r="AF8" cm="1">
+        <f t="array" aca="1" ref="AF8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
         <v>1.6585341205040181</v>
       </c>
-      <c r="AF8" cm="1">
-        <f t="array" aca="1" ref="AF8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
+      <c r="AG8" cm="1">
+        <f t="array" aca="1" ref="AG8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
         <v>1.4650856811858359</v>
       </c>
-      <c r="AG8" cm="1">
-        <f t="array" aca="1" ref="AG8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
+      <c r="AH8" cm="1">
+        <f t="array" aca="1" ref="AH8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
         <v>5.6562457469554204</v>
       </c>
-      <c r="AH8" cm="1">
-        <f t="array" aca="1" ref="AH8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
+      <c r="AI8" cm="1">
+        <f t="array" aca="1" ref="AI8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
         <v>1.9897581518347631</v>
       </c>
-      <c r="AI8" cm="1">
-        <f t="array" aca="1" ref="AI8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AI:AI))</f>
-        <v>0.72249620855714503</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" cm="1">
+        <f t="array" aca="1" ref="D9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
+        <v>32.079368014915858</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
+        <v>42.424051795715833</v>
+      </c>
+      <c r="F9" cm="1">
+        <f t="array" aca="1" ref="F9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!E:E))</f>
+        <v>41.337958340458592</v>
+      </c>
+      <c r="G9" cm="1">
+        <f t="array" aca="1" ref="G9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!F:F))</f>
+        <v>41.860192869653623</v>
+      </c>
+      <c r="H9" cm="1">
+        <f t="array" aca="1" ref="H9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
+        <v>42.491091411943891</v>
+      </c>
+      <c r="I9" cm="1">
+        <f t="array" aca="1" ref="I9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
+        <v>42.856940327743928</v>
+      </c>
+      <c r="J9" cm="1">
+        <f t="array" aca="1" ref="J9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
+        <v>42.836404449860076</v>
+      </c>
+      <c r="K9" cm="1">
+        <f t="array" aca="1" ref="K9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!J:J))</f>
+        <v>43.332715462560728</v>
+      </c>
+      <c r="L9" cm="1">
+        <f t="array" aca="1" ref="L9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
+        <v>43.604720306671609</v>
+      </c>
+      <c r="M9" cm="1">
+        <f t="array" aca="1" ref="M9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
+        <v>41.80329560651829</v>
+      </c>
+      <c r="N9" cm="1">
+        <f t="array" aca="1" ref="N9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
+        <v>36.774870879083451</v>
+      </c>
+      <c r="O9" cm="1">
+        <f t="array" aca="1" ref="O9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
+        <v>36.645657057615843</v>
+      </c>
+      <c r="P9" cm="1">
+        <f t="array" aca="1" ref="P9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!O:O))</f>
+        <v>30.802554884829213</v>
+      </c>
+      <c r="Q9" cm="1">
+        <f t="array" aca="1" ref="Q9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
+        <v>33.834226973164498</v>
+      </c>
+      <c r="R9" cm="1">
+        <f t="array" aca="1" ref="R9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
+        <v>34.060836113885657</v>
+      </c>
+      <c r="S9" cm="1">
+        <f t="array" aca="1" ref="S9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
+        <v>40.535006057331017</v>
+      </c>
+      <c r="T9" cm="1">
+        <f t="array" aca="1" ref="T9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
+        <v>13.811183056022397</v>
+      </c>
+      <c r="U9" cm="1">
+        <f t="array" aca="1" ref="U9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
+        <v>0.16414232588538388</v>
+      </c>
+      <c r="V9" cm="1">
+        <f t="array" aca="1" ref="V9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
+        <v>0.157447052848011</v>
+      </c>
+      <c r="W9" cm="1">
+        <f t="array" aca="1" ref="W9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
+        <v>0.14754486425261068</v>
+      </c>
+      <c r="X9" cm="1">
+        <f t="array" aca="1" ref="X9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
+        <v>30.002650253454799</v>
+      </c>
+      <c r="Y9" cm="1">
+        <f t="array" aca="1" ref="Y9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
+        <v>41.120151822793233</v>
+      </c>
+      <c r="Z9" cm="1">
+        <f t="array" aca="1" ref="Z9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
+        <v>39.63970730353067</v>
+      </c>
+      <c r="AA9" cm="1">
+        <f t="array" aca="1" ref="AA9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Z:Z))</f>
+        <v>40.160519554830302</v>
+      </c>
+      <c r="AB9" cm="1">
+        <f t="array" aca="1" ref="AB9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AA:AA))</f>
+        <v>40.839335054177624</v>
+      </c>
+      <c r="AC9" cm="1">
+        <f t="array" aca="1" ref="AC9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AB:AB))</f>
+        <v>41.28381500167847</v>
+      </c>
+      <c r="AD9" cm="1">
+        <f t="array" aca="1" ref="AD9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
+        <v>41.247639059736834</v>
+      </c>
+      <c r="AE9" cm="1">
+        <f t="array" aca="1" ref="AE9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
+        <v>41.367348876835628</v>
+      </c>
+      <c r="AF9" cm="1">
+        <f t="array" aca="1" ref="AF9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
+        <v>41.6226923984349</v>
+      </c>
+      <c r="AG9" cm="1">
+        <f t="array" aca="1" ref="AG9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
+        <v>39.804132509174863</v>
+      </c>
+      <c r="AH9" cm="1">
+        <f t="array" aca="1" ref="AH9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
+        <v>34.526476206053822</v>
+      </c>
+      <c r="AI9" cm="1">
+        <f t="array" aca="1" ref="AI9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
+        <v>34.375212294342475</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2529,7 +2686,7 @@
       <c r="AM13" s="8"/>
       <c r="AN13" s="8"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -2572,7 +2729,7 @@
       <c r="AM14" s="8"/>
       <c r="AN14" s="8"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
         <v>7</v>
       </c>
@@ -2615,7 +2772,7 @@
       <c r="AM15" s="8"/>
       <c r="AN15" s="8"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -2658,7 +2815,7 @@
       <c r="AM16" s="8"/>
       <c r="AN16" s="8"/>
     </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>9</v>
       </c>
@@ -2702,82 +2859,94 @@
         <v>22</v>
       </c>
       <c r="P17" s="8">
+        <v>2022</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>2023</v>
+      </c>
+      <c r="R17" s="8">
+        <v>2024</v>
+      </c>
+      <c r="S17" s="8">
+        <v>2025</v>
+      </c>
+      <c r="T17" s="8">
         <v>2026</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="U17" s="8">
         <v>2027</v>
       </c>
-      <c r="R17" s="8">
+      <c r="V17" s="8">
         <v>2028</v>
       </c>
-      <c r="S17" s="8">
+      <c r="W17" s="8">
         <v>2029</v>
       </c>
-      <c r="T17" s="8">
+      <c r="X17" s="8">
         <v>2030</v>
       </c>
-      <c r="U17" s="8">
+      <c r="Y17" s="8">
         <v>2031</v>
       </c>
-      <c r="V17" s="8">
+      <c r="Z17" s="8">
         <v>2032</v>
       </c>
-      <c r="W17" s="8">
+      <c r="AA17" s="8">
         <v>2033</v>
       </c>
-      <c r="X17" s="8">
+      <c r="AB17" s="8">
         <v>2034</v>
       </c>
-      <c r="Y17" s="8">
+      <c r="AC17" s="8">
         <v>2035</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="AD17" s="8">
         <v>2036</v>
       </c>
-      <c r="AA17" s="8">
+      <c r="AE17" s="8">
         <v>2037</v>
       </c>
-      <c r="AB17" s="8">
+      <c r="AF17" s="8">
         <v>2038</v>
       </c>
-      <c r="AC17" s="8">
+      <c r="AG17" s="8">
         <v>2039</v>
       </c>
-      <c r="AD17" s="8">
+      <c r="AH17" s="8">
         <v>2040</v>
       </c>
-      <c r="AE17" s="8">
+      <c r="AI17" s="8">
         <v>2041</v>
       </c>
-      <c r="AF17" s="8">
+      <c r="AJ17" s="8">
         <v>2042</v>
       </c>
-      <c r="AG17" s="8">
+      <c r="AK17" s="8">
         <v>2043</v>
       </c>
-      <c r="AH17" s="8">
+      <c r="AL17" s="8">
         <v>2044</v>
       </c>
-      <c r="AI17" s="8">
+      <c r="AM17" s="8">
         <v>2045</v>
       </c>
-      <c r="AJ17" s="8">
+      <c r="AN17" s="8">
         <v>2046</v>
       </c>
-      <c r="AK17" s="8">
+      <c r="AO17" s="8">
         <v>2047</v>
       </c>
-      <c r="AL17" s="8">
+      <c r="AP17" s="8">
         <v>2048</v>
       </c>
-      <c r="AM17" s="8">
+      <c r="AQ17" s="8">
         <v>2049</v>
       </c>
-      <c r="AN17" s="8">
+      <c r="AR17" s="8">
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="str">
         <f>+A3</f>
         <v>RSD-SHALLOW</v>
@@ -2797,16 +2966,16 @@
       <c r="N18" s="8">
         <v>5</v>
       </c>
-      <c r="P18" s="16">
-        <f ca="1">+K3*$O$13</f>
+      <c r="P18" s="16" cm="1">
+        <f t="array" aca="1" ref="P18" ca="1">+SUM(D3:G3*$O$13)</f>
+        <v>13.669525477577253</v>
+      </c>
+      <c r="Q18" s="16">
+        <f ca="1">+H3*$O$13</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="16">
-        <f t="shared" ref="Q18:AN23" ca="1" si="0">+L3*$O$13</f>
-        <v>0</v>
-      </c>
       <c r="R18" s="16">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="Q18:S19" ca="1" si="0">+I3*$O$13</f>
         <v>0</v>
       </c>
       <c r="S18" s="16">
@@ -2814,97 +2983,113 @@
         <v>0</v>
       </c>
       <c r="T18" s="16">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">+K3*$O$13</f>
         <v>0</v>
       </c>
       <c r="U18" s="16">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="U18:AR23" ca="1" si="1">+L3*$O$13</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.43574332617179445</v>
       </c>
-      <c r="V18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AA18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.45125958973832125</v>
       </c>
-      <c r="W18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AB18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.45125962127154284</v>
       </c>
-      <c r="X18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3721891393380576</v>
       </c>
-      <c r="Y18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AD18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3721890624076707</v>
       </c>
-      <c r="Z18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AE18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877039535008957</v>
       </c>
-      <c r="AA18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AF18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053323342512</v>
       </c>
-      <c r="AB18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AG18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053450341155</v>
       </c>
-      <c r="AC18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AH18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.387705330621253</v>
       </c>
-      <c r="AD18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AI18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053475813863</v>
       </c>
-      <c r="AE18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AJ18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053473266723</v>
       </c>
-      <c r="AF18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AK18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053438994138</v>
       </c>
-      <c r="AG18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AL18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053401224635</v>
       </c>
-      <c r="AH18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AM18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053379208393</v>
       </c>
-      <c r="AI18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AN18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053316611159</v>
       </c>
-      <c r="AJ18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AO18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.387705341224402</v>
       </c>
-      <c r="AK18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AP18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053559185013</v>
       </c>
-      <c r="AL18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AQ18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053537109076</v>
       </c>
-      <c r="AM18" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AR18" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.3877053432826361</v>
       </c>
-      <c r="AN18" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.3877053691241632</v>
-      </c>
-    </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="str">
-        <f t="shared" ref="B19:B23" si="1">+A4</f>
+        <f t="shared" ref="B19:B23" si="2">+A4</f>
         <v>RSD-DEEP</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" ref="D19:D23" si="2">+C4</f>
+        <f t="shared" ref="D19:D22" si="3">+C4</f>
         <v>R-RTFT-Apt_E, R-RTFT-Apt_F, R-RTFT-Apt_G, R-RTFT-Att_E, R-RTFT-Att_F, R-RTFT-Att_G, R-RTFT-Det_E, R-RTFT-Det_F, R-RTFT-Det_G</v>
       </c>
       <c r="J19" s="8" t="s">
@@ -2918,114 +3103,130 @@
       <c r="N19" s="8">
         <v>5</v>
       </c>
-      <c r="P19" s="16">
-        <f t="shared" ref="P19:P23" ca="1" si="3">+K4*$O$13</f>
-        <v>7.2442793937117305</v>
+      <c r="P19" s="16" cm="1">
+        <f t="array" aca="1" ref="P19" ca="1">+SUM(D4:G4*$O$13)/2</f>
+        <v>32.777952743636547</v>
       </c>
       <c r="Q19" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.0506432768517922</v>
+        <f ca="1">P19</f>
+        <v>32.777952743636547</v>
       </c>
       <c r="R19" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>3.0506432771560599</v>
+        <v>0</v>
       </c>
       <c r="S19" s="16">
         <f t="shared" ca="1" si="0"/>
+        <v>7.1022243705981589</v>
+      </c>
+      <c r="T19" s="16">
+        <f t="shared" ref="T19:T23" ca="1" si="4">+K4*$O$13</f>
+        <v>21.917662154267131</v>
+      </c>
+      <c r="U19" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.2442793937117305</v>
+      </c>
+      <c r="V19" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.0506432768517922</v>
+      </c>
+      <c r="W19" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.0506432771560599</v>
+      </c>
+      <c r="X19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.68323515278444369</v>
       </c>
-      <c r="T19" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Y19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="U19" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Z19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.1032522095427104E-2</v>
       </c>
-      <c r="V19" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AA19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.5516272572890753E-2</v>
       </c>
-      <c r="W19" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AB19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.5516264955051854E-2</v>
       </c>
-      <c r="X19" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.5516222470601256E-2</v>
       </c>
-      <c r="Y19" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AD19" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.5516303451877059E-2</v>
       </c>
-      <c r="Z19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AE19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AF19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AG19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AH19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AI19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AJ19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AK19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AL19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AM19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AN19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AO19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AP19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AL19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AQ19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="16">
-        <f t="shared" si="0"/>
+      <c r="AR19" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RSD-APT-HP</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>R-HC_Apt_ELC_HPN1, R-HC_Apt_ELC_HPN2-AB, R-HC_Apt_ELC_HPN2-C, R-HC_Apt_ELC_HPN2-D, R-HC_Apt_ELC_HPN2-E, R-HC_Apt_ELC_HPN2-F, R-HC_Apt_ELC_HPN2-G, R-SH_Apt_ELC_HPN1, R-SH_Apt_ELC_HPN2-AB, R-SH_Apt_ELC_HPN2-C, R-SH_Apt_ELC_HPN2-D, R-SH_Apt_ELC_HPN2-E, R-SH_Apt_ELC_HPN2-F, R-SH_Apt_ELC_HPN2-G, R-SH_Apt_ELC_HPN3-AB, R-SH_Apt_ELC_HPN3-C, R-SH_Apt_ELC_HPN3-D, R-SH_Apt_ELC_HPN3-E, R-SH_Apt_ELC_HPN3-F, R-SH_Apt_ELC_HPN3-G, R-SW_Apt_ELC_HPN1-AB, R-SW_Apt_ELC_HPN1-C, R-SW_Apt_ELC_HPN1-D, R-SW_Apt_ELC_HPN1-E, R-SW_Apt_ELC_HPN1-F, R-SW_Apt_ELC_HPN1-G, R-SW_Apt_GAS_HHPN1, R-SW_Apt_GAS_HPN1, R-SW_Apt_GAS_HPN2</v>
       </c>
       <c r="J20" s="8" t="s">
@@ -3037,114 +3238,118 @@
       <c r="N20" s="8">
         <v>5</v>
       </c>
-      <c r="P20" s="16">
-        <f t="shared" ca="1" si="3"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16">
+        <f t="shared" ca="1" si="4"/>
+        <v>16.774075463491776</v>
+      </c>
+      <c r="U20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>9.9204134270921493E-2</v>
       </c>
-      <c r="Q20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="V20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>9.531648475009806E-2</v>
       </c>
-      <c r="R20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="W20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>8.9997078869308161E-2</v>
       </c>
-      <c r="S20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="X20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>8.4698997802605633E-2</v>
       </c>
-      <c r="T20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Y20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.9724559508503262E-3</v>
       </c>
-      <c r="U20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Z20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.31583438384637108</v>
       </c>
-      <c r="V20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AA20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.13306813682875607</v>
       </c>
-      <c r="W20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AB20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.972291084586463E-3</v>
       </c>
-      <c r="Y20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AD20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AE20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AF20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AG20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AH20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AI20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AJ20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="16">
-        <f t="shared" si="0"/>
+      <c r="AK20" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AL20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.4914080802839087</v>
       </c>
-      <c r="AH20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AM20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>17.664021771529377</v>
       </c>
-      <c r="AI20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AN20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>19.036208150242398</v>
       </c>
-      <c r="AJ20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AO20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.2470030863136537</v>
       </c>
-      <c r="AK20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AP20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.2432569068781707</v>
       </c>
-      <c r="AL20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AQ20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.23767942012693913</v>
       </c>
-      <c r="AM20" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AR20" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.2319985453786014</v>
       </c>
-      <c r="AN20" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RSD-BIOGAS</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>R-SH_Apt_GAS_N1,R-SH_Att_GAS_N1,R-SH_Det_GAS_N1,R-SW_Apt_GAS_HHPN1,R-SW_Apt_GAS_HPN1,R-SW_Apt_GAS_HPN2,R-SW_Apt_GAS_N1,R-SW_Att_GAS_HHPN1,R-SW_Att_GAS_HPN1,R-SW_Att_GAS_HPN2,R-SW_Att_GAS_N1,R-SW_Att_GAS_N2,R-SW_Att_GAS_N3,R-SW_Det_GAS_HHPN1,R-SW_Det_GAS_HPN1,R-SW_Det_GAS_HPN2,R-SW_Det_GAS_N1,R-SW_Det_GAS_N2,R-SW_Det_GAS_N3</v>
       </c>
       <c r="J21" s="8" t="s">
@@ -3156,114 +3361,118 @@
       <c r="N21" s="8">
         <v>5</v>
       </c>
-      <c r="P21" s="16">
-        <f t="shared" ca="1" si="3"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="U21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="R21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="V21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="W21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="T21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="X21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="U21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Y21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="V21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Z21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="W21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AA21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="X21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AB21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AD21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AE21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AF21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AG21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AH21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AI21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AJ21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AK21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AL21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AM21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AN21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AO21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AP21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AM21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AQ21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AR21" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RSD-ATT-HP</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>R-HC_Att_ELC_HPN1, R-HC_Att_ELC_HPN2-AB, R-HC_Att_ELC_HPN2-C, R-HC_Att_ELC_HPN2-D, R-HC_Att_ELC_HPN2-E, R-HC_Att_ELC_HPN2-F, R-HC_Att_ELC_HPN2-G, R-SH_Att_ELC_HPN1, R-SH_Att_ELC_HPN2-AB, R-SH_Att_ELC_HPN2-C, R-SH_Att_ELC_HPN2-D, R-SH_Att_ELC_HPN2-E, R-SH_Att_ELC_HPN2-F, R-SH_Att_ELC_HPN2-G, R-SH_Att_ELC_HPN3-AB, R-SH_Att_ELC_HPN3-C, R-SH_Att_ELC_HPN3-D, R-SH_Att_ELC_HPN3-E, R-SH_Att_ELC_HPN3-F, R-SH_Att_ELC_HPN3-G, R-SW_Att_ELC_HPN1-AB, R-SW_Att_ELC_HPN1-C, R-SW_Att_ELC_HPN1-D, R-SW_Att_ELC_HPN1-E, R-SW_Att_ELC_HPN1-F, R-SW_Att_ELC_HPN1-G, R-SW_Att_ELC_HPN2-AB, R-SW_Att_ELC_HPN2-C, R-SW_Att_ELC_HPN2-D, R-SW_Att_ELC_HPN2-E, R-SW_Att_ELC_HPN2-F, R-SW_Att_ELC_HPN2-G, R-SW_Att_GAS_HHPN1, R-SW_Att_GAS_HPN1, R-SW_Att_GAS_HPN2</v>
       </c>
       <c r="J22" s="8" t="s">
@@ -3276,109 +3485,125 @@
         <v>5</v>
       </c>
       <c r="P22" s="16">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ref="P22:P23" ca="1" si="5">+G7*$O$13</f>
+        <v>47.213008302896405</v>
+      </c>
+      <c r="Q22" s="16">
+        <f t="shared" ref="Q22:Q23" ca="1" si="6">+H7*$O$13</f>
+        <v>46.308950440410605</v>
+      </c>
+      <c r="R22" s="16">
+        <f t="shared" ref="R22:R23" ca="1" si="7">+I7*$O$13</f>
+        <v>35.614397619333189</v>
+      </c>
+      <c r="S22" s="16">
+        <f t="shared" ref="S22:S23" ca="1" si="8">+J7*$O$13</f>
+        <v>33.321198928814731</v>
+      </c>
+      <c r="T22" s="16">
+        <f t="shared" ca="1" si="4"/>
+        <v>19.435703035331169</v>
+      </c>
+      <c r="U22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.57096154589297043</v>
       </c>
-      <c r="Q22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="V22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.6116695612369123</v>
       </c>
-      <c r="R22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="W22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.62049544045153793</v>
       </c>
-      <c r="S22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="X22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.6195318366937772</v>
       </c>
-      <c r="T22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Y22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.45546988786755388</v>
       </c>
-      <c r="U22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Z22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>4.6392334435066784</v>
       </c>
-      <c r="V22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AA22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>4.389216739331709</v>
       </c>
-      <c r="W22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AB22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.53170186775750239</v>
       </c>
-      <c r="X22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.50857249413498296</v>
       </c>
-      <c r="Y22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AD22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>10.395609603288078</v>
       </c>
-      <c r="Z22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AE22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>10.470400799540503</v>
       </c>
-      <c r="AA22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AF22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>11.171745089155172</v>
       </c>
-      <c r="AB22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AG22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>11.868080130489137</v>
       </c>
-      <c r="AC22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AH22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>58.676456516380284</v>
       </c>
-      <c r="AD22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AI22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>46.506278363865235</v>
       </c>
-      <c r="AE22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AJ22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>46.542816879679727</v>
       </c>
-      <c r="AF22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AK22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>45.893847583157765</v>
       </c>
-      <c r="AG22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AL22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>35.183543881381119</v>
       </c>
-      <c r="AH22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AM22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>32.873766814670958</v>
       </c>
-      <c r="AI22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AN22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>18.980237090942328</v>
       </c>
-      <c r="AJ22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AO22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.2420314727300572</v>
       </c>
-      <c r="AK22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AP22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.90619858498628281</v>
       </c>
-      <c r="AL22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AQ22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.1298436191402619</v>
       </c>
-      <c r="AM22" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AR22" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.93683029993920508</v>
       </c>
-      <c r="AN22" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.62808464464308456</v>
-      </c>
-    </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f>+A8</f>
         <v>RSD-DH</v>
       </c>
       <c r="D23" t="s">
@@ -3394,116 +3619,263 @@
         <v>5</v>
       </c>
       <c r="P23" s="16">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="16">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.30361430101391618</v>
+      </c>
+      <c r="R23" s="16">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.5018297946164343</v>
+      </c>
+      <c r="S23" s="16">
+        <f t="shared" ca="1" si="8"/>
+        <v>1.4064685256963387</v>
+      </c>
+      <c r="T23" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.87531242844283008</v>
       </c>
-      <c r="Q23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="V23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.70776756805145924</v>
       </c>
-      <c r="R23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="W23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>4.8232405696409693</v>
       </c>
-      <c r="S23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="X23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.2405208054727834</v>
       </c>
-      <c r="T23" s="16">
-        <f t="shared" si="0"/>
+      <c r="Y23" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="Z23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>2.6435467048233234</v>
       </c>
-      <c r="V23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AA23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.4308275190318431</v>
       </c>
-      <c r="W23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AB23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.5994983087000461</v>
       </c>
-      <c r="X23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.601279945541104</v>
       </c>
-      <c r="Y23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AD23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.6076718848378246</v>
       </c>
-      <c r="Z23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AE23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.6234637185653549</v>
       </c>
-      <c r="AA23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AF23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>3.6333082049955543</v>
       </c>
-      <c r="AB23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AG23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.61637501870996869</v>
       </c>
-      <c r="AC23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AH23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.49552146077618664</v>
       </c>
-      <c r="AD23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AI23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.1427459792766016</v>
       </c>
-      <c r="AE23" s="16">
-        <f t="shared" si="0"/>
+      <c r="AJ23" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF23" s="16">
-        <f t="shared" si="0"/>
+      <c r="AK23" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="16">
-        <f t="shared" si="0"/>
+      <c r="AL23" s="16">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AM23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.3195385199119063</v>
       </c>
-      <c r="AI23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AN23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>0.71006953510619664</v>
       </c>
-      <c r="AJ23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AO23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.6253634380939377</v>
       </c>
-      <c r="AK23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AP23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.4357839675621191</v>
       </c>
-      <c r="AL23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AQ23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>5.5431208320163119</v>
       </c>
-      <c r="AM23" s="16">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AR23" s="16">
+        <f t="shared" ca="1" si="1"/>
         <v>1.9499629887980678</v>
       </c>
-      <c r="AN23" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.70804628438600214</v>
-      </c>
-    </row>
-    <row r="24" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B24" s="8"/>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="B24" s="8" t="str">
+        <f>+A9</f>
+        <v>RSD_BLD-DET-HP</v>
+      </c>
+      <c r="D24" t="s">
+        <v>185</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="8">
+        <v>1</v>
+      </c>
+      <c r="N24" s="8">
+        <v>5</v>
+      </c>
+      <c r="P24">
+        <f ca="1">+G9</f>
+        <v>41.860192869653623</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" ref="Q24:AR24" ca="1" si="9">+H9</f>
+        <v>42.491091411943891</v>
+      </c>
+      <c r="R24">
+        <f t="shared" ca="1" si="9"/>
+        <v>42.856940327743928</v>
+      </c>
+      <c r="S24">
+        <f t="shared" ca="1" si="9"/>
+        <v>42.836404449860076</v>
+      </c>
+      <c r="T24">
+        <f t="shared" ca="1" si="9"/>
+        <v>43.332715462560728</v>
+      </c>
+      <c r="U24">
+        <f t="shared" ca="1" si="9"/>
+        <v>43.604720306671609</v>
+      </c>
+      <c r="V24">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.80329560651829</v>
+      </c>
+      <c r="W24">
+        <f t="shared" ca="1" si="9"/>
+        <v>36.774870879083451</v>
+      </c>
+      <c r="X24">
+        <f t="shared" ca="1" si="9"/>
+        <v>36.645657057615843</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" ca="1" si="9"/>
+        <v>30.802554884829213</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" ca="1" si="9"/>
+        <v>33.834226973164498</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" ca="1" si="9"/>
+        <v>34.060836113885657</v>
+      </c>
+      <c r="AB24">
+        <f t="shared" ca="1" si="9"/>
+        <v>40.535006057331017</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" ca="1" si="9"/>
+        <v>13.811183056022397</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.16414232588538388</v>
+      </c>
+      <c r="AE24">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.157447052848011</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.14754486425261068</v>
+      </c>
+      <c r="AG24">
+        <f t="shared" ca="1" si="9"/>
+        <v>30.002650253454799</v>
+      </c>
+      <c r="AH24">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.120151822793233</v>
+      </c>
+      <c r="AI24">
+        <f t="shared" ca="1" si="9"/>
+        <v>39.63970730353067</v>
+      </c>
+      <c r="AJ24">
+        <f t="shared" ca="1" si="9"/>
+        <v>40.160519554830302</v>
+      </c>
+      <c r="AK24">
+        <f t="shared" ca="1" si="9"/>
+        <v>40.839335054177624</v>
+      </c>
+      <c r="AL24">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.28381500167847</v>
+      </c>
+      <c r="AM24">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.247639059736834</v>
+      </c>
+      <c r="AN24">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.367348876835628</v>
+      </c>
+      <c r="AO24">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.6226923984349</v>
+      </c>
+      <c r="AP24">
+        <f t="shared" ca="1" si="9"/>
+        <v>39.804132509174863</v>
+      </c>
+      <c r="AQ24">
+        <f t="shared" ca="1" si="9"/>
+        <v>34.526476206053822</v>
+      </c>
+      <c r="AR24">
+        <f t="shared" ca="1" si="9"/>
+        <v>34.375212294342475</v>
+      </c>
+    </row>
+    <row r="25" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B25" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D3:AI8">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+  <phoneticPr fontId="28" type="noConversion"/>
+  <conditionalFormatting sqref="D3:AI9">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0.001</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3513,14 +3885,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB842C1C-4194-41D2-89A9-1D7E416B4493}">
-  <dimension ref="A1:AI141"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI148"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3531,7 +3903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3638,7 +4010,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -3745,7 +4117,7 @@
         <v>2.9276261944037E-7</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -3852,7 +4224,7 @@
         <v>6.2344680916243996E-7</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -3897,7 +4269,7 @@
         <v>1.38728280425417E-8</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -4004,7 +4376,7 @@
         <v>26.345319960574098</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -4107,7 +4479,7 @@
         <v>2.37417519261952E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
@@ -4210,7 +4582,7 @@
         <v>2.4130221508066299E-8</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
@@ -4313,7 +4685,7 @@
         <v>5.3692020542095E-8</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -4414,7 +4786,7 @@
         <v>3.8617672335569503E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
@@ -4509,7 +4881,7 @@
         <v>3.4204854866921698E-8</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -4598,7 +4970,7 @@
         <v>3.0495473529944798E-8</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -4681,7 +5053,7 @@
         <v>2.5476863520809199E-8</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
@@ -4754,7 +5126,7 @@
         <v>1.5361089085736701E-8</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
@@ -4853,7 +5225,7 @@
         <v>2.5833628581428199E-8</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
@@ -4912,7 +5284,7 @@
         <v>1.6931259063296699E-8</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
@@ -4969,7 +5341,7 @@
         <v>1.61270938109049E-8</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -5026,7 +5398,7 @@
         <v>1.5350818948180001E-8</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
@@ -5113,7 +5485,7 @@
         <v>2.8556410602626698E-8</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -5196,7 +5568,7 @@
         <v>2.7281445610762001E-8</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
@@ -5283,7 +5655,7 @@
         <v>2.85837034114053E-8</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
@@ -5350,7 +5722,7 @@
         <v>2.0517308317224301E-8</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -5415,7 +5787,7 @@
         <v>1.98825594177308E-8</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>29</v>
       </c>
@@ -5478,7 +5850,7 @@
         <v>2.1258453962934698E-8</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -5585,7 +5957,7 @@
         <v>6.2344680916243996E-7</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
@@ -5630,7 +6002,7 @@
         <v>1.38728280425417E-8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
@@ -5737,7 +6109,7 @@
         <v>5.5039640329224402E-8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -5840,7 +6212,7 @@
         <v>4.8405508112332502E-8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
@@ -5943,7 +6315,7 @@
         <v>3.2876273053768699E-8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
@@ -6046,7 +6418,7 @@
         <v>0.36124810429336002</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>48</v>
       </c>
@@ -6149,7 +6521,7 @@
         <v>0.36124810426378501</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
@@ -6256,7 +6628,7 @@
         <v>9.7539060100496095E-8</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>48</v>
       </c>
@@ -6359,7 +6731,7 @@
         <v>5.8633931159297101E-8</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>48</v>
       </c>
@@ -6462,7 +6834,7 @@
         <v>3.5518628999374102E-8</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>57</v>
       </c>
@@ -6569,7 +6941,7 @@
         <v>3.34748050636036E-7</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>57</v>
       </c>
@@ -6676,7 +7048,7 @@
         <v>8.64573346059189E-7</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>57</v>
       </c>
@@ -6727,7 +7099,7 @@
         <v>1.7097348365783902E-8</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>57</v>
       </c>
@@ -6834,7 +7206,7 @@
         <v>1.8256939861213899E-6</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
@@ -6921,7 +7293,7 @@
         <v>4.3729979846871798E-8</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>57</v>
       </c>
@@ -7028,7 +7400,7 @@
         <v>5.7887707510361198E-8</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>64</v>
       </c>
@@ -7135,7 +7507,7 @@
         <v>0.64089884338420799</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>64</v>
       </c>
@@ -7242,7 +7614,7 @@
         <v>2.38715262175896E-8</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>64</v>
       </c>
@@ -7349,7 +7721,7 @@
         <v>1.6195951627016899E-7</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>64</v>
       </c>
@@ -7456,7 +7828,7 @@
         <v>1.29040577017814E-7</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>64</v>
       </c>
@@ -7563,7 +7935,7 @@
         <v>1.02884221804871E-7</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>64</v>
       </c>
@@ -7670,7 +8042,7 @@
         <v>8.5857671464263097E-8</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>64</v>
       </c>
@@ -7723,7 +8095,7 @@
         <v>1.8692620871293799E-8</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>64</v>
       </c>
@@ -7770,7 +8142,7 @@
         <v>1.33236260932352E-8</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>64</v>
       </c>
@@ -7815,7 +8187,7 @@
         <v>1.25189871678222E-8</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>64</v>
       </c>
@@ -7860,7 +8232,7 @@
         <v>1.2118294382059899E-8</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>64</v>
       </c>
@@ -7903,7 +8275,7 @@
         <v>1.17464468323764E-8</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>64</v>
       </c>
@@ -7986,7 +8358,7 @@
         <v>5.1211136243806203E-8</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>64</v>
       </c>
@@ -8067,7 +8439,7 @@
         <v>3.3864823473746698E-8</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>64</v>
       </c>
@@ -8140,7 +8512,7 @@
         <v>3.1491972776790801E-8</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>64</v>
       </c>
@@ -8209,7 +8581,7 @@
         <v>2.8010536418604E-8</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>64</v>
       </c>
@@ -8276,7 +8648,7 @@
         <v>2.7040685109087801E-8</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>64</v>
       </c>
@@ -8339,7 +8711,7 @@
         <v>2.61316478522303E-8</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
@@ -8446,7 +8818,7 @@
         <v>5.7826192445498002E-7</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>64</v>
       </c>
@@ -8553,7 +8925,7 @@
         <v>4.0088818084145799E-7</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>64</v>
       </c>
@@ -8660,7 +9032,7 @@
         <v>3.9509064721441002E-7</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>64</v>
       </c>
@@ -8767,7 +9139,7 @@
         <v>3.6544188416232902E-7</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>64</v>
       </c>
@@ -8874,7 +9246,7 @@
         <v>3.5652913303401998E-7</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>64</v>
       </c>
@@ -8981,7 +9353,7 @@
         <v>3.4802622205606599E-7</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
@@ -9088,7 +9460,7 @@
         <v>8.64573346059189E-7</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
@@ -9139,7 +9511,7 @@
         <v>1.7097348365783902E-8</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>88</v>
       </c>
@@ -9186,7 +9558,7 @@
         <v>1.14359473278138E-8</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>88</v>
       </c>
@@ -9293,7 +9665,7 @@
         <v>1.3979290759314601E-7</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>88</v>
       </c>
@@ -9388,7 +9760,7 @@
         <v>6.1773177638577702E-8</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>88</v>
       </c>
@@ -9479,7 +9851,7 @@
         <v>5.9639871036427597E-8</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>88</v>
       </c>
@@ -9544,7 +9916,7 @@
         <v>1.5353687607562898E-8</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>88</v>
       </c>
@@ -9589,7 +9961,7 @@
         <v>1.34471369925899E-8</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>88</v>
       </c>
@@ -9696,7 +10068,7 @@
         <v>25.6556969499952</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>88</v>
       </c>
@@ -9803,7 +10175,7 @@
         <v>25.6556969115044</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>88</v>
       </c>
@@ -9908,7 +10280,7 @@
         <v>2.1841159698607701E-7</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>88</v>
       </c>
@@ -9999,7 +10371,7 @@
         <v>8.7515918236056497E-8</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>88</v>
       </c>
@@ -10070,7 +10442,7 @@
         <v>2.4867434067231499E-8</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>88</v>
       </c>
@@ -10115,7 +10487,7 @@
         <v>1.12728810012841E-8</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>88</v>
       </c>
@@ -10202,7 +10574,7 @@
         <v>6.6810589238385703E-8</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>88</v>
       </c>
@@ -10281,7 +10653,7 @@
         <v>1.62124219849899E-8</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>103</v>
       </c>
@@ -10384,7 +10756,7 @@
         <v>1.15625086846683E-7</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>103</v>
       </c>
@@ -10491,7 +10863,7 @@
         <v>8.9958493694149599E-7</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>103</v>
       </c>
@@ -10550,7 +10922,7 @@
         <v>1.6594631038694601E-8</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>103</v>
       </c>
@@ -10657,7 +11029,7 @@
         <v>10.6124126669445</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>103</v>
       </c>
@@ -10750,7 +11122,7 @@
         <v>3.3339214119456203E-8</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>103</v>
       </c>
@@ -10857,7 +11229,7 @@
         <v>3.8263619003980001E-8</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>110</v>
       </c>
@@ -10964,7 +11336,7 @@
         <v>3.4079543821511303E-8</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>110</v>
       </c>
@@ -11071,7 +11443,7 @@
         <v>1.8596059595957501E-8</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>110</v>
       </c>
@@ -11178,7 +11550,7 @@
         <v>8.0072290675408095E-8</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>110</v>
       </c>
@@ -11285,7 +11657,7 @@
         <v>29.3206550316151</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>110</v>
       </c>
@@ -11392,7 +11764,7 @@
         <v>1.0530482765080101E-7</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>110</v>
       </c>
@@ -11499,7 +11871,7 @@
         <v>3.8055174727453503E-8</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>110</v>
       </c>
@@ -11554,7 +11926,7 @@
         <v>1.3751454578610901E-8</v>
       </c>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>110</v>
       </c>
@@ -11631,7 +12003,7 @@
         <v>-3.4536481415138899E-7</v>
       </c>
     </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>110</v>
       </c>
@@ -11702,7 +12074,7 @@
       </c>
       <c r="AI94" s="6"/>
     </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>110</v>
       </c>
@@ -11771,7 +12143,7 @@
         <v>1.06587449177478E-8</v>
       </c>
     </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>110</v>
       </c>
@@ -11836,7 +12208,7 @@
       </c>
       <c r="AI96" s="6"/>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>110</v>
       </c>
@@ -11901,7 +12273,7 @@
       </c>
       <c r="AI97" s="6"/>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>110</v>
       </c>
@@ -11982,7 +12354,7 @@
         <v>4.5850981304886798E-8</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>110</v>
       </c>
@@ -12059,7 +12431,7 @@
         <v>3.17500035677006E-8</v>
       </c>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>110</v>
       </c>
@@ -12134,7 +12506,7 @@
         <v>2.9931967705968801E-8</v>
       </c>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>110</v>
       </c>
@@ -12207,7 +12579,7 @@
         <v>2.72821943456455E-8</v>
       </c>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>110</v>
       </c>
@@ -12280,7 +12652,7 @@
         <v>2.6155861404411799E-8</v>
       </c>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>110</v>
       </c>
@@ -12353,7 +12725,7 @@
         <v>2.4913737872745701E-8</v>
       </c>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>110</v>
       </c>
@@ -12460,7 +12832,7 @@
         <v>5.1308409486057797E-7</v>
       </c>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>110</v>
       </c>
@@ -12567,7 +12939,7 @@
         <v>3.6854963965962899E-7</v>
       </c>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>110</v>
       </c>
@@ -12674,7 +13046,7 @@
         <v>3.6736157099014902E-7</v>
       </c>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>110</v>
       </c>
@@ -12781,7 +13153,7 @@
         <v>3.4679343290262298E-7</v>
       </c>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>110</v>
       </c>
@@ -12888,7 +13260,7 @@
         <v>3.3521409730565399E-7</v>
       </c>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>110</v>
       </c>
@@ -12995,7 +13367,7 @@
         <v>3.21187700750945E-7</v>
       </c>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
@@ -13102,7 +13474,7 @@
         <v>8.9958493694149599E-7</v>
       </c>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>110</v>
       </c>
@@ -13161,7 +13533,7 @@
         <v>1.6594631038694601E-8</v>
       </c>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>135</v>
       </c>
@@ -13206,7 +13578,7 @@
         <v>1.1202546423463801E-8</v>
       </c>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>135</v>
       </c>
@@ -13297,7 +13669,7 @@
         <v>6.1851716541714699E-8</v>
       </c>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>135</v>
       </c>
@@ -13380,7 +13752,7 @@
         <v>4.2902810978011898E-8</v>
       </c>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>135</v>
       </c>
@@ -13463,7 +13835,7 @@
         <v>3.5768004935687102E-8</v>
       </c>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>135</v>
       </c>
@@ -13514,7 +13886,7 @@
         <v>1.1618876324439499E-8</v>
       </c>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>135</v>
       </c>
@@ -13581,7 +13953,7 @@
         <v>1.38053363603909E-8</v>
       </c>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>135</v>
       </c>
@@ -13688,7 +14060,7 @@
         <v>9.7436451039399295E-8</v>
       </c>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>135</v>
       </c>
@@ -13775,7 +14147,7 @@
         <v>8.2118010267464594E-8</v>
       </c>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>135</v>
       </c>
@@ -13830,7 +14202,7 @@
         <v>1.81404722487046E-8</v>
       </c>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>135</v>
       </c>
@@ -13875,7 +14247,7 @@
       <c r="AH121" s="6"/>
       <c r="AI121" s="6"/>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>135</v>
       </c>
@@ -13960,7 +14332,7 @@
         <v>4.5994102665324899E-8</v>
       </c>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>135</v>
       </c>
@@ -14019,7 +14391,7 @@
         <v>1.1998312701122701E-8</v>
       </c>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>148</v>
       </c>
@@ -14068,7 +14440,7 @@
         <v>4.4609943742344597E-8</v>
       </c>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>148</v>
       </c>
@@ -14117,7 +14489,7 @@
         <v>4.2503969682107097E-8</v>
       </c>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>148</v>
       </c>
@@ -14202,7 +14574,7 @@
         <v>0.476301723116409</v>
       </c>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>148</v>
       </c>
@@ -14247,7 +14619,7 @@
         <v>1.64945320072844E-8</v>
       </c>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>148</v>
       </c>
@@ -14298,7 +14670,7 @@
         <v>1.5715784687223301E-8</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>148</v>
       </c>
@@ -14397,7 +14769,7 @@
         <v>6.7255276663617106E-8</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>148</v>
       </c>
@@ -14474,7 +14846,7 @@
         <v>1.96013174319261</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>148</v>
       </c>
@@ -14551,7 +14923,7 @@
         <v>3.40050840175113E-7</v>
       </c>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>148</v>
       </c>
@@ -14602,7 +14974,7 @@
         <v>3.30983956644373E-8</v>
       </c>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>148</v>
       </c>
@@ -14649,7 +15021,7 @@
       <c r="AH133" s="6"/>
       <c r="AI133" s="6"/>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>148</v>
       </c>
@@ -14700,7 +15072,7 @@
       <c r="AH134" s="6"/>
       <c r="AI134" s="6"/>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>148</v>
       </c>
@@ -14759,7 +15131,7 @@
         <v>1.5743746751152199E-8</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>148</v>
       </c>
@@ -14810,7 +15182,7 @@
         <v>6.3199901340324095E-8</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>148</v>
       </c>
@@ -14861,7 +15233,7 @@
         <v>6.0354627544003797E-8</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>148</v>
       </c>
@@ -14928,7 +15300,7 @@
         <v>1.8267010389501499</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>148</v>
       </c>
@@ -14975,7 +15347,7 @@
         <v>1.24704889938966E-8</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>148</v>
       </c>
@@ -15028,7 +15400,7 @@
       <c r="AH140" s="6"/>
       <c r="AI140" s="6"/>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>148</v>
       </c>
@@ -15089,6 +15461,12 @@
         <v>1.16397577785782E-8</v>
       </c>
     </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="str">
+        <f>+_xlfn.TEXTJOIN(", ",TRUE,B86:B111)</f>
+        <v>R-SH_Det_ELC_HPN2-AB, R-SH_Det_ELC_HPN2-C, R-SH_Det_ELC_HPN2-D, R-SH_Det_ELC_HPN2-E, R-SH_Det_ELC_HPN2-F, R-SH_Det_ELC_HPN2-G, R-SH_Det_ELC_HPN3-AB, R-SH_Det_ELC_HPN3-C, R-SH_Det_ELC_HPN3-D, R-SH_Det_ELC_HPN3-E, R-SH_Det_ELC_HPN3-F, R-SH_Det_ELC_HPN3-G, R-SW_Det_ELC_HPN1-AB, R-SW_Det_ELC_HPN1-C, R-SW_Det_ELC_HPN1-D, R-SW_Det_ELC_HPN1-E, R-SW_Det_ELC_HPN1-F, R-SW_Det_ELC_HPN1-G, R-SW_Det_ELC_HPN2-AB, R-SW_Det_ELC_HPN2-C, R-SW_Det_ELC_HPN2-D, R-SW_Det_ELC_HPN2-E, R-SW_Det_ELC_HPN2-F, R-SW_Det_ELC_HPN2-G, R-SW_Det_GAS_HHPN1, R-SW_Det_GAS_HPN1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SuppXLS/Scen_z_MACC-RSD-CAPs.xlsx
+++ b/SuppXLS/Scen_z_MACC-RSD-CAPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3648DC4-7B5E-4D5A-A228-875D5325D9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35CC729-9DE8-498D-B921-5E832AA21533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="185">
   <si>
     <t>Sum of Pv</t>
   </si>
@@ -581,9 +581,6 @@
   </si>
   <si>
     <t>District Heating</t>
-  </si>
-  <si>
-    <t>R-SW_Apt_HET_N1, R-SW_Apt_HET_N2</t>
   </si>
   <si>
     <t>RSD-SHALLOW</t>
@@ -623,11 +620,18 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1173,205 +1177,206 @@
   </borders>
   <cellStyleXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="41"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="41"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="45"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="165"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="43" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="165" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="45"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="165"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="43" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="165" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="165" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="165" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="165" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="167"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="165" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="165" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="167"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyFont="1"/>
   </cellXfs>
   <cellStyles count="168">
     <cellStyle name="20 % - Akzent1" xfId="72" hidden="1" xr:uid="{64AE4B0C-66F8-4587-9F6C-91708716F8BF}"/>
@@ -1692,21 +1697,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR25"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.109375" bestFit="1"/>
+    <col min="1" max="2" width="17.08984375" bestFit="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="35" width="17.109375" bestFit="1"/>
+    <col min="4" max="35" width="17.08984375" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
       <c r="D2" s="4">
         <v>2019</v>
       </c>
@@ -1804,9 +1809,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>167</v>
@@ -1943,9 +1948,9 @@
         <v>2.4364340237577919</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>169</v>
@@ -2022,15 +2027,15 @@
         <v>1.5832962705996999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>171</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C5,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
@@ -2113,9 +2118,9 @@
         <v>0.23673320957000143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>172</v>
@@ -2252,15 +2257,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>171</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C7,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
@@ -2391,118 +2396,118 @@
         <v>0.95594928565225012</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>175</v>
+      <c r="C8" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="D8" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
-        <v>0</v>
+        <v>9.0735479411977593</v>
       </c>
       <c r="E8" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!D:D))</f>
-        <v>0</v>
+        <v>4.1711694799231599E-7</v>
       </c>
       <c r="H8" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!G:G))</f>
-        <v>0.30981051123868997</v>
+        <v>1.4875295008633831</v>
       </c>
       <c r="I8" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!H:H))</f>
-        <v>3.5732957087922799</v>
+        <v>15.710625201055469</v>
       </c>
       <c r="J8" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!I:I))</f>
-        <v>1.435171964996264</v>
+        <v>15.598123770076024</v>
       </c>
       <c r="L8" cm="1">
         <f t="array" aca="1" ref="L8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!K:K))</f>
-        <v>0.89317594739064299</v>
+        <v>18.013096156998515</v>
       </c>
       <c r="M8" cm="1">
         <f t="array" aca="1" ref="M8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!L:L))</f>
-        <v>0.7222118041341421</v>
+        <v>14.024978698769212</v>
       </c>
       <c r="N8" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!M:M))</f>
-        <v>4.9216740506540502</v>
+        <v>14.186424801293441</v>
       </c>
       <c r="O8" cm="1">
         <f t="array" aca="1" ref="O8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!N:N))</f>
-        <v>1.2658375566048812</v>
+        <v>8.1557917365004826</v>
       </c>
       <c r="Q8" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!P:P))</f>
-        <v>2.6974966375748197</v>
+        <v>17.639958458024907</v>
       </c>
       <c r="R8" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Q:Q))</f>
-        <v>3.5008444071753502</v>
+        <v>46.833301327557052</v>
       </c>
       <c r="S8" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!R:R))</f>
-        <v>3.6729574578571897</v>
+        <v>38.786988137203494</v>
       </c>
       <c r="T8" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!S:S))</f>
-        <v>3.6747754546337799</v>
+        <v>41.796395180446083</v>
       </c>
       <c r="U8" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!T:T))</f>
-        <v>3.6812978416712498</v>
+        <v>40.98754347872795</v>
       </c>
       <c r="V8" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!U:U))</f>
-        <v>3.69741195771975</v>
+        <v>40.86738982658585</v>
       </c>
       <c r="W8" cm="1">
         <f t="array" aca="1" ref="W8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!V:V))</f>
-        <v>3.7074573520362799</v>
+        <v>40.035766439199179</v>
       </c>
       <c r="X8" cm="1">
         <f t="array" aca="1" ref="X8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!W:W))</f>
-        <v>0.6289541007244579</v>
+        <v>53.437352303890457</v>
       </c>
       <c r="Y8" cm="1">
         <f t="array" aca="1" ref="Y8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!X:X))</f>
-        <v>0.50563414364917003</v>
+        <v>0.50563569090127314</v>
       </c>
       <c r="Z8" cm="1">
         <f t="array" aca="1" ref="Z8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!Y:Y))</f>
-        <v>0.1456591625271445</v>
+        <v>1.4708089072971564</v>
       </c>
       <c r="AD8" cm="1">
         <f t="array" aca="1" ref="AD8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AC:AC))</f>
-        <v>1.3464678774611289</v>
+        <v>1.3464766539622166</v>
       </c>
       <c r="AE8" cm="1">
         <f t="array" aca="1" ref="AE8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AD:AD))</f>
-        <v>0.72456075010836396</v>
+        <v>0.72456578127978899</v>
       </c>
       <c r="AF8" cm="1">
         <f t="array" aca="1" ref="AF8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AE:AE))</f>
-        <v>1.6585341205040181</v>
+        <v>23.593098494611418</v>
       </c>
       <c r="AG8" cm="1">
         <f t="array" aca="1" ref="AG8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AF:AF))</f>
-        <v>1.4650856811858359</v>
+        <v>19.697020950063965</v>
       </c>
       <c r="AH8" cm="1">
         <f t="array" aca="1" ref="AH8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AG:AG))</f>
-        <v>5.6562457469554204</v>
+        <v>18.244628946664871</v>
       </c>
       <c r="AI8" cm="1">
         <f t="array" aca="1" ref="AI8" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C8,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!AH:AH))</f>
-        <v>1.9897581518347631</v>
-      </c>
-    </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+        <v>14.103936363659892</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -2510,7 +2515,7 @@
         <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D9" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">SUMPRODUCT(SUMIF(caps_data!$B:$B,TRIM(MID(SUBSTITUTE($C9,", ",REPT(" ",100)),(ROW(INDIRECT("1:50"))-1)*100+1,100)),caps_data!C:C))</f>
@@ -2641,7 +2646,7 @@
         <v>34.375212294342475</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2686,7 +2691,7 @@
       <c r="AM13" s="8"/>
       <c r="AN13" s="8"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -2729,7 +2734,7 @@
       <c r="AM14" s="8"/>
       <c r="AN14" s="8"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B15" s="9" t="s">
         <v>7</v>
       </c>
@@ -2772,7 +2777,7 @@
       <c r="AM15" s="8"/>
       <c r="AN15" s="8"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -2815,7 +2820,7 @@
       <c r="AM16" s="8"/>
       <c r="AN16" s="8"/>
     </row>
-    <row r="17" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B17" s="13" t="s">
         <v>9</v>
       </c>
@@ -2946,7 +2951,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B18" s="8" t="str">
         <f>+A3</f>
         <v>RSD-SHALLOW</v>
@@ -2975,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="16">
-        <f t="shared" ref="Q18:S19" ca="1" si="0">+I3*$O$13</f>
+        <f t="shared" ref="R18:S19" ca="1" si="0">+I3*$O$13</f>
         <v>0</v>
       </c>
       <c r="S18" s="16">
@@ -3083,9 +3088,9 @@
         <v>2.3877053432826361</v>
       </c>
     </row>
-    <row r="19" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="str">
-        <f t="shared" ref="B19:B23" si="2">+A4</f>
+        <f t="shared" ref="B19:B22" si="2">+A4</f>
         <v>RSD-DEEP</v>
       </c>
       <c r="D19" t="str">
@@ -3220,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="str">
         <f t="shared" si="2"/>
         <v>RSD-APT-HP</v>
@@ -3343,7 +3348,7 @@
         <v>0.2319985453786014</v>
       </c>
     </row>
-    <row r="21" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B21" s="8" t="str">
         <f t="shared" si="2"/>
         <v>RSD-BIOGAS</v>
@@ -3466,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B22" s="8" t="str">
         <f t="shared" si="2"/>
         <v>RSD-ATT-HP</v>
@@ -3601,13 +3606,13 @@
         <v>0.93683029993920508</v>
       </c>
     </row>
-    <row r="23" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="str">
         <f>+A8</f>
         <v>RSD-DH</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>23</v>
@@ -3624,15 +3629,15 @@
       </c>
       <c r="Q23" s="16">
         <f t="shared" ca="1" si="6"/>
-        <v>0.30361430101391618</v>
+        <v>1.4577789108461154</v>
       </c>
       <c r="R23" s="16">
         <f t="shared" ca="1" si="7"/>
-        <v>3.5018297946164343</v>
+        <v>15.396412697034361</v>
       </c>
       <c r="S23" s="16">
         <f t="shared" ca="1" si="8"/>
-        <v>1.4064685256963387</v>
+        <v>15.286161294674503</v>
       </c>
       <c r="T23" s="16">
         <f t="shared" si="4"/>
@@ -3640,19 +3645,19 @@
       </c>
       <c r="U23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87531242844283008</v>
+        <v>17.652834233858545</v>
       </c>
       <c r="V23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.70776756805145924</v>
+        <v>13.744479124793827</v>
       </c>
       <c r="W23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>4.8232405696409693</v>
+        <v>13.902696305267572</v>
       </c>
       <c r="X23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2405208054727834</v>
+        <v>7.9926759017704727</v>
       </c>
       <c r="Y23" s="16">
         <f t="shared" si="1"/>
@@ -3660,43 +3665,43 @@
       </c>
       <c r="Z23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6435467048233234</v>
+        <v>17.287159288864409</v>
       </c>
       <c r="AA23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4308275190318431</v>
+        <v>45.896635301005908</v>
       </c>
       <c r="AB23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>3.5994983087000461</v>
+        <v>38.01124837445942</v>
       </c>
       <c r="AC23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>3.601279945541104</v>
+        <v>40.960467276837164</v>
       </c>
       <c r="AD23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6076718848378246</v>
+        <v>40.167792609153388</v>
       </c>
       <c r="AE23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6234637185653549</v>
+        <v>40.050042030054129</v>
       </c>
       <c r="AF23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6333082049955543</v>
+        <v>39.235051110415192</v>
       </c>
       <c r="AG23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.61637501870996869</v>
+        <v>52.368605257812646</v>
       </c>
       <c r="AH23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.49552146077618664</v>
+        <v>0.49552297708324766</v>
       </c>
       <c r="AI23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.1427459792766016</v>
+        <v>1.4413927291512132</v>
       </c>
       <c r="AJ23" s="16">
         <f t="shared" si="1"/>
@@ -3712,36 +3717,36 @@
       </c>
       <c r="AM23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3195385199119063</v>
+        <v>1.3195471208829723</v>
       </c>
       <c r="AN23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71006953510619664</v>
+        <v>0.71007446565419319</v>
       </c>
       <c r="AO23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6253634380939377</v>
+        <v>23.12123652471919</v>
       </c>
       <c r="AP23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>1.4357839675621191</v>
+        <v>19.303080531062687</v>
       </c>
       <c r="AQ23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>5.5431208320163119</v>
+        <v>17.879736367731574</v>
       </c>
       <c r="AR23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>1.9499629887980678</v>
-      </c>
-    </row>
-    <row r="24" spans="2:44" x14ac:dyDescent="0.3">
+        <v>13.821857636386694</v>
+      </c>
+    </row>
+    <row r="24" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B24" s="8" t="str">
         <f>+A9</f>
         <v>RSD_BLD-DET-HP</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>23</v>
@@ -3869,11 +3874,11 @@
         <v>34.375212294342475</v>
       </c>
     </row>
-    <row r="25" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B25" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="29" type="noConversion"/>
   <conditionalFormatting sqref="D3:AI9">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0.001</formula>
@@ -3886,13 +3891,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB842C1C-4194-41D2-89A9-1D7E416B4493}">
   <dimension ref="A1:AI148"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.36328125" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3903,7 +3908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -4010,7 +4015,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -4117,7 +4122,7 @@
         <v>2.9276261944037E-7</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -4224,7 +4229,7 @@
         <v>6.2344680916243996E-7</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -4269,7 +4274,7 @@
         <v>1.38728280425417E-8</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -4376,7 +4381,7 @@
         <v>26.345319960574098</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -4479,7 +4484,7 @@
         <v>2.37417519261952E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
@@ -4582,7 +4587,7 @@
         <v>2.4130221508066299E-8</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
@@ -4685,7 +4690,7 @@
         <v>5.3692020542095E-8</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -4786,7 +4791,7 @@
         <v>3.8617672335569503E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
@@ -4881,7 +4886,7 @@
         <v>3.4204854866921698E-8</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -4970,7 +4975,7 @@
         <v>3.0495473529944798E-8</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -5053,7 +5058,7 @@
         <v>2.5476863520809199E-8</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
@@ -5126,7 +5131,7 @@
         <v>1.5361089085736701E-8</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
@@ -5225,7 +5230,7 @@
         <v>2.5833628581428199E-8</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
@@ -5284,7 +5289,7 @@
         <v>1.6931259063296699E-8</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
@@ -5341,7 +5346,7 @@
         <v>1.61270938109049E-8</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -5398,7 +5403,7 @@
         <v>1.5350818948180001E-8</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
@@ -5485,7 +5490,7 @@
         <v>2.8556410602626698E-8</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -5568,7 +5573,7 @@
         <v>2.7281445610762001E-8</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
@@ -5655,7 +5660,7 @@
         <v>2.85837034114053E-8</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
@@ -5722,7 +5727,7 @@
         <v>2.0517308317224301E-8</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -5787,7 +5792,7 @@
         <v>1.98825594177308E-8</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>29</v>
       </c>
@@ -5850,7 +5855,7 @@
         <v>2.1258453962934698E-8</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -5957,7 +5962,7 @@
         <v>6.2344680916243996E-7</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
@@ -6002,7 +6007,7 @@
         <v>1.38728280425417E-8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
@@ -6109,7 +6114,7 @@
         <v>5.5039640329224402E-8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -6212,7 +6217,7 @@
         <v>4.8405508112332502E-8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
@@ -6315,7 +6320,7 @@
         <v>3.2876273053768699E-8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
@@ -6418,7 +6423,7 @@
         <v>0.36124810429336002</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>48</v>
       </c>
@@ -6521,7 +6526,7 @@
         <v>0.36124810426378501</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
@@ -6628,7 +6633,7 @@
         <v>9.7539060100496095E-8</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>48</v>
       </c>
@@ -6731,7 +6736,7 @@
         <v>5.8633931159297101E-8</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>48</v>
       </c>
@@ -6834,7 +6839,7 @@
         <v>3.5518628999374102E-8</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>57</v>
       </c>
@@ -6941,7 +6946,7 @@
         <v>3.34748050636036E-7</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>57</v>
       </c>
@@ -7048,7 +7053,7 @@
         <v>8.64573346059189E-7</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>57</v>
       </c>
@@ -7099,7 +7104,7 @@
         <v>1.7097348365783902E-8</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>57</v>
       </c>
@@ -7206,7 +7211,7 @@
         <v>1.8256939861213899E-6</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
@@ -7293,7 +7298,7 @@
         <v>4.3729979846871798E-8</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>57</v>
       </c>
@@ -7400,7 +7405,7 @@
         <v>5.7887707510361198E-8</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>64</v>
       </c>
@@ -7507,7 +7512,7 @@
         <v>0.64089884338420799</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>64</v>
       </c>
@@ -7614,7 +7619,7 @@
         <v>2.38715262175896E-8</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>64</v>
       </c>
@@ -7721,7 +7726,7 @@
         <v>1.6195951627016899E-7</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>64</v>
       </c>
@@ -7828,7 +7833,7 @@
         <v>1.29040577017814E-7</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>64</v>
       </c>
@@ -7935,7 +7940,7 @@
         <v>1.02884221804871E-7</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>64</v>
       </c>
@@ -8042,7 +8047,7 @@
         <v>8.5857671464263097E-8</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>64</v>
       </c>
@@ -8095,7 +8100,7 @@
         <v>1.8692620871293799E-8</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>64</v>
       </c>
@@ -8142,7 +8147,7 @@
         <v>1.33236260932352E-8</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>64</v>
       </c>
@@ -8187,7 +8192,7 @@
         <v>1.25189871678222E-8</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>64</v>
       </c>
@@ -8232,7 +8237,7 @@
         <v>1.2118294382059899E-8</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>64</v>
       </c>
@@ -8275,7 +8280,7 @@
         <v>1.17464468323764E-8</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>64</v>
       </c>
@@ -8358,7 +8363,7 @@
         <v>5.1211136243806203E-8</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>64</v>
       </c>
@@ -8439,7 +8444,7 @@
         <v>3.3864823473746698E-8</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>64</v>
       </c>
@@ -8512,7 +8517,7 @@
         <v>3.1491972776790801E-8</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>64</v>
       </c>
@@ -8581,7 +8586,7 @@
         <v>2.8010536418604E-8</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>64</v>
       </c>
@@ -8648,7 +8653,7 @@
         <v>2.7040685109087801E-8</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>64</v>
       </c>
@@ -8711,7 +8716,7 @@
         <v>2.61316478522303E-8</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
@@ -8818,7 +8823,7 @@
         <v>5.7826192445498002E-7</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>64</v>
       </c>
@@ -8925,7 +8930,7 @@
         <v>4.0088818084145799E-7</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>64</v>
       </c>
@@ -9032,7 +9037,7 @@
         <v>3.9509064721441002E-7</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>64</v>
       </c>
@@ -9139,7 +9144,7 @@
         <v>3.6544188416232902E-7</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>64</v>
       </c>
@@ -9246,7 +9251,7 @@
         <v>3.5652913303401998E-7</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>64</v>
       </c>
@@ -9353,7 +9358,7 @@
         <v>3.4802622205606599E-7</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
@@ -9460,7 +9465,7 @@
         <v>8.64573346059189E-7</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
@@ -9511,7 +9516,7 @@
         <v>1.7097348365783902E-8</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>88</v>
       </c>
@@ -9558,7 +9563,7 @@
         <v>1.14359473278138E-8</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>88</v>
       </c>
@@ -9665,7 +9670,7 @@
         <v>1.3979290759314601E-7</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>88</v>
       </c>
@@ -9760,7 +9765,7 @@
         <v>6.1773177638577702E-8</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>88</v>
       </c>
@@ -9851,7 +9856,7 @@
         <v>5.9639871036427597E-8</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>88</v>
       </c>
@@ -9916,7 +9921,7 @@
         <v>1.5353687607562898E-8</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>88</v>
       </c>
@@ -9961,7 +9966,7 @@
         <v>1.34471369925899E-8</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>88</v>
       </c>
@@ -10068,7 +10073,7 @@
         <v>25.6556969499952</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>88</v>
       </c>
@@ -10175,7 +10180,7 @@
         <v>25.6556969115044</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>88</v>
       </c>
@@ -10280,7 +10285,7 @@
         <v>2.1841159698607701E-7</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>88</v>
       </c>
@@ -10371,7 +10376,7 @@
         <v>8.7515918236056497E-8</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>88</v>
       </c>
@@ -10442,7 +10447,7 @@
         <v>2.4867434067231499E-8</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>88</v>
       </c>
@@ -10487,7 +10492,7 @@
         <v>1.12728810012841E-8</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>88</v>
       </c>
@@ -10574,7 +10579,7 @@
         <v>6.6810589238385703E-8</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>88</v>
       </c>
@@ -10653,7 +10658,7 @@
         <v>1.62124219849899E-8</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>103</v>
       </c>
@@ -10756,7 +10761,7 @@
         <v>1.15625086846683E-7</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>103</v>
       </c>
@@ -10863,7 +10868,7 @@
         <v>8.9958493694149599E-7</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>103</v>
       </c>
@@ -10922,7 +10927,7 @@
         <v>1.6594631038694601E-8</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>103</v>
       </c>
@@ -11029,7 +11034,7 @@
         <v>10.6124126669445</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>103</v>
       </c>
@@ -11122,7 +11127,7 @@
         <v>3.3339214119456203E-8</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>103</v>
       </c>
@@ -11229,7 +11234,7 @@
         <v>3.8263619003980001E-8</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>110</v>
       </c>
@@ -11336,7 +11341,7 @@
         <v>3.4079543821511303E-8</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>110</v>
       </c>
@@ -11443,7 +11448,7 @@
         <v>1.8596059595957501E-8</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>110</v>
       </c>
@@ -11550,7 +11555,7 @@
         <v>8.0072290675408095E-8</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>110</v>
       </c>
@@ -11657,7 +11662,7 @@
         <v>29.3206550316151</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>110</v>
       </c>
@@ -11764,7 +11769,7 @@
         <v>1.0530482765080101E-7</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>110</v>
       </c>
@@ -11871,7 +11876,7 @@
         <v>3.8055174727453503E-8</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>110</v>
       </c>
@@ -11926,7 +11931,7 @@
         <v>1.3751454578610901E-8</v>
       </c>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>110</v>
       </c>
@@ -12003,7 +12008,7 @@
         <v>-3.4536481415138899E-7</v>
       </c>
     </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>110</v>
       </c>
@@ -12074,7 +12079,7 @@
       </c>
       <c r="AI94" s="6"/>
     </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>110</v>
       </c>
@@ -12143,7 +12148,7 @@
         <v>1.06587449177478E-8</v>
       </c>
     </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>110</v>
       </c>
@@ -12208,7 +12213,7 @@
       </c>
       <c r="AI96" s="6"/>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>110</v>
       </c>
@@ -12273,7 +12278,7 @@
       </c>
       <c r="AI97" s="6"/>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>110</v>
       </c>
@@ -12354,7 +12359,7 @@
         <v>4.5850981304886798E-8</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>110</v>
       </c>
@@ -12431,7 +12436,7 @@
         <v>3.17500035677006E-8</v>
       </c>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>110</v>
       </c>
@@ -12506,7 +12511,7 @@
         <v>2.9931967705968801E-8</v>
       </c>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>110</v>
       </c>
@@ -12579,7 +12584,7 @@
         <v>2.72821943456455E-8</v>
       </c>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>110</v>
       </c>
@@ -12652,7 +12657,7 @@
         <v>2.6155861404411799E-8</v>
       </c>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>110</v>
       </c>
@@ -12725,7 +12730,7 @@
         <v>2.4913737872745701E-8</v>
       </c>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>110</v>
       </c>
@@ -12832,7 +12837,7 @@
         <v>5.1308409486057797E-7</v>
       </c>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>110</v>
       </c>
@@ -12939,7 +12944,7 @@
         <v>3.6854963965962899E-7</v>
       </c>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>110</v>
       </c>
@@ -13046,7 +13051,7 @@
         <v>3.6736157099014902E-7</v>
       </c>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>110</v>
       </c>
@@ -13153,7 +13158,7 @@
         <v>3.4679343290262298E-7</v>
       </c>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>110</v>
       </c>
@@ -13260,7 +13265,7 @@
         <v>3.3521409730565399E-7</v>
       </c>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>110</v>
       </c>
@@ -13367,7 +13372,7 @@
         <v>3.21187700750945E-7</v>
       </c>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
@@ -13474,7 +13479,7 @@
         <v>8.9958493694149599E-7</v>
       </c>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>110</v>
       </c>
@@ -13533,7 +13538,7 @@
         <v>1.6594631038694601E-8</v>
       </c>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>135</v>
       </c>
@@ -13578,7 +13583,7 @@
         <v>1.1202546423463801E-8</v>
       </c>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>135</v>
       </c>
@@ -13669,7 +13674,7 @@
         <v>6.1851716541714699E-8</v>
       </c>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>135</v>
       </c>
@@ -13752,7 +13757,7 @@
         <v>4.2902810978011898E-8</v>
       </c>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>135</v>
       </c>
@@ -13835,7 +13840,7 @@
         <v>3.5768004935687102E-8</v>
       </c>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>135</v>
       </c>
@@ -13886,7 +13891,7 @@
         <v>1.1618876324439499E-8</v>
       </c>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>135</v>
       </c>
@@ -13953,7 +13958,7 @@
         <v>1.38053363603909E-8</v>
       </c>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>135</v>
       </c>
@@ -14060,7 +14065,7 @@
         <v>9.7436451039399295E-8</v>
       </c>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>135</v>
       </c>
@@ -14147,7 +14152,7 @@
         <v>8.2118010267464594E-8</v>
       </c>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>135</v>
       </c>
@@ -14202,7 +14207,7 @@
         <v>1.81404722487046E-8</v>
       </c>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>135</v>
       </c>
@@ -14247,7 +14252,7 @@
       <c r="AH121" s="6"/>
       <c r="AI121" s="6"/>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>135</v>
       </c>
@@ -14332,7 +14337,7 @@
         <v>4.5994102665324899E-8</v>
       </c>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>135</v>
       </c>
@@ -14391,7 +14396,7 @@
         <v>1.1998312701122701E-8</v>
       </c>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>148</v>
       </c>
@@ -14440,7 +14445,7 @@
         <v>4.4609943742344597E-8</v>
       </c>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>148</v>
       </c>
@@ -14489,7 +14494,7 @@
         <v>4.2503969682107097E-8</v>
       </c>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>148</v>
       </c>
@@ -14574,7 +14579,7 @@
         <v>0.476301723116409</v>
       </c>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>148</v>
       </c>
@@ -14619,7 +14624,7 @@
         <v>1.64945320072844E-8</v>
       </c>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>148</v>
       </c>
@@ -14670,7 +14675,7 @@
         <v>1.5715784687223301E-8</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>148</v>
       </c>
@@ -14769,7 +14774,7 @@
         <v>6.7255276663617106E-8</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>148</v>
       </c>
@@ -14846,7 +14851,7 @@
         <v>1.96013174319261</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>148</v>
       </c>
@@ -14923,7 +14928,7 @@
         <v>3.40050840175113E-7</v>
       </c>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>148</v>
       </c>
@@ -14974,7 +14979,7 @@
         <v>3.30983956644373E-8</v>
       </c>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>148</v>
       </c>
@@ -15021,7 +15026,7 @@
       <c r="AH133" s="6"/>
       <c r="AI133" s="6"/>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>148</v>
       </c>
@@ -15072,7 +15077,7 @@
       <c r="AH134" s="6"/>
       <c r="AI134" s="6"/>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>148</v>
       </c>
@@ -15131,7 +15136,7 @@
         <v>1.5743746751152199E-8</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>148</v>
       </c>
@@ -15182,7 +15187,7 @@
         <v>6.3199901340324095E-8</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>148</v>
       </c>
@@ -15233,7 +15238,7 @@
         <v>6.0354627544003797E-8</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>148</v>
       </c>
@@ -15300,7 +15305,7 @@
         <v>1.8267010389501499</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>148</v>
       </c>
@@ -15347,7 +15352,7 @@
         <v>1.24704889938966E-8</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>148</v>
       </c>
@@ -15400,7 +15405,7 @@
       <c r="AH140" s="6"/>
       <c r="AI140" s="6"/>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>148</v>
       </c>
@@ -15461,7 +15466,7 @@
         <v>1.16397577785782E-8</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" t="str">
         <f>+_xlfn.TEXTJOIN(", ",TRUE,B86:B111)</f>
         <v>R-SH_Det_ELC_HPN2-AB, R-SH_Det_ELC_HPN2-C, R-SH_Det_ELC_HPN2-D, R-SH_Det_ELC_HPN2-E, R-SH_Det_ELC_HPN2-F, R-SH_Det_ELC_HPN2-G, R-SH_Det_ELC_HPN3-AB, R-SH_Det_ELC_HPN3-C, R-SH_Det_ELC_HPN3-D, R-SH_Det_ELC_HPN3-E, R-SH_Det_ELC_HPN3-F, R-SH_Det_ELC_HPN3-G, R-SW_Det_ELC_HPN1-AB, R-SW_Det_ELC_HPN1-C, R-SW_Det_ELC_HPN1-D, R-SW_Det_ELC_HPN1-E, R-SW_Det_ELC_HPN1-F, R-SW_Det_ELC_HPN1-G, R-SW_Det_ELC_HPN2-AB, R-SW_Det_ELC_HPN2-C, R-SW_Det_ELC_HPN2-D, R-SW_Det_ELC_HPN2-E, R-SW_Det_ELC_HPN2-F, R-SW_Det_ELC_HPN2-G, R-SW_Det_GAS_HHPN1, R-SW_Det_GAS_HPN1</v>
